--- a/REGEN/Contour_Maelstrom.xlsx
+++ b/REGEN/Contour_Maelstrom.xlsx
@@ -85,7 +85,7 @@
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.00062749449081803002</v>
+        <v>0.00062749449081803003</v>
       </c>
       <c r="B3" s="0">
         <v>0.042227500000000001</v>
@@ -272,7 +272,7 @@
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.0059611976627712854</v>
+        <v>0.0059611976627712855</v>
       </c>
       <c r="B20" s="0">
         <v>0.042227500000000001</v>
@@ -778,7 +778,7 @@
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>0.020393570951585976</v>
+        <v>0.020393570951585977</v>
       </c>
       <c r="B66" s="0">
         <v>0.042227500000000001</v>
@@ -844,7 +844,7 @@
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.022276054424040063</v>
+        <v>0.022276054424040064</v>
       </c>
       <c r="B72" s="0">
         <v>0.042227500000000001</v>
@@ -1141,7 +1141,7 @@
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.030747230050083472</v>
+        <v>0.030747230050083473</v>
       </c>
       <c r="B99" s="0">
         <v>0.042227500000000001</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="187">
       <c r="A187" s="0">
-        <v>0.058356987646076781</v>
+        <v>0.058356987646076782</v>
       </c>
       <c r="B187" s="0">
         <v>0.042227500000000001</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="226">
       <c r="A226" s="0">
-        <v>0.070593130217028371</v>
+        <v>0.070593130217028372</v>
       </c>
       <c r="B226" s="0">
         <v>0.042227500000000001</v>
@@ -2571,7 +2571,7 @@
     </row>
     <row r="229">
       <c r="A229" s="0">
-        <v>0.071534371953255418</v>
+        <v>0.071534371953255419</v>
       </c>
       <c r="B229" s="0">
         <v>0.042227500000000001</v>
@@ -2703,7 +2703,7 @@
     </row>
     <row r="241">
       <c r="A241" s="0">
-        <v>0.075299338898163592</v>
+        <v>0.075299338898163593</v>
       </c>
       <c r="B241" s="0">
         <v>0.042227500000000001</v>
@@ -2736,7 +2736,7 @@
     </row>
     <row r="244">
       <c r="A244" s="0">
-        <v>0.076240580634390639</v>
+        <v>0.07624058063439064</v>
       </c>
       <c r="B244" s="0">
         <v>0.042227500000000001</v>
@@ -2769,7 +2769,7 @@
     </row>
     <row r="247">
       <c r="A247" s="0">
-        <v>0.077181822370617686</v>
+        <v>0.077181822370617687</v>
       </c>
       <c r="B247" s="0">
         <v>0.042227500000000001</v>
@@ -2802,7 +2802,7 @@
     </row>
     <row r="250">
       <c r="A250" s="0">
-        <v>0.078123064106844733</v>
+        <v>0.078123064106844734</v>
       </c>
       <c r="B250" s="0">
         <v>0.042227500000000001</v>
@@ -2835,7 +2835,7 @@
     </row>
     <row r="253">
       <c r="A253" s="0">
-        <v>0.07906430584307178</v>
+        <v>0.079064305843071781</v>
       </c>
       <c r="B253" s="0">
         <v>0.042227500000000001</v>
@@ -2868,7 +2868,7 @@
     </row>
     <row r="256">
       <c r="A256" s="0">
-        <v>0.080005547579298827</v>
+        <v>0.080005547579298828</v>
       </c>
       <c r="B256" s="0">
         <v>0.042227500000000001</v>
@@ -3512,7 +3512,7 @@
         <v>0.042203368288967008</v>
       </c>
       <c r="C314" s="0">
-        <v>6.3425806917742253</v>
+        <v>6.3425806917742254</v>
       </c>
     </row>
     <row r="315">
@@ -3520,7 +3520,7 @@
         <v>0.09851663505843071</v>
       </c>
       <c r="B315" s="0">
-        <v>0.042180095081803939</v>
+        <v>0.04218009508180394</v>
       </c>
       <c r="C315" s="0">
         <v>6.3355873403087175</v>
@@ -3531,7 +3531,7 @@
         <v>0.098830382303839726</v>
       </c>
       <c r="B316" s="0">
-        <v>0.042148982205388381</v>
+        <v>0.042148982205388382</v>
       </c>
       <c r="C316" s="0">
         <v>6.3262442771244309</v>
@@ -3567,7 +3567,7 @@
         <v>0.042007945397639204</v>
       </c>
       <c r="C319" s="0">
-        <v>6.2839779884431239</v>
+        <v>6.283977988443124</v>
       </c>
     </row>
     <row r="320">
@@ -3578,7 +3578,7 @@
         <v>0.041944732759688685</v>
       </c>
       <c r="C320" s="0">
-        <v>6.2650802321928047</v>
+        <v>6.2650802321928048</v>
       </c>
     </row>
     <row r="321">
@@ -3619,7 +3619,7 @@
         <v>0.10134036026711184</v>
       </c>
       <c r="B324" s="0">
-        <v>0.041607381252213554</v>
+        <v>0.041607381252213555</v>
       </c>
       <c r="C324" s="0">
         <v>6.1647083954616138</v>
@@ -3696,7 +3696,7 @@
         <v>0.10353659098497495</v>
       </c>
       <c r="B331" s="0">
-        <v>0.040657711779351353</v>
+        <v>0.040657711779351354</v>
       </c>
       <c r="C331" s="0">
         <v>5.8865066537798594</v>
@@ -3960,7 +3960,7 @@
         <v>0.11106652487479129</v>
       </c>
       <c r="B355" s="0">
-        <v>0.033841838842068261</v>
+        <v>0.033841838842068262</v>
       </c>
       <c r="C355" s="0">
         <v>4.0783047910023162</v>
@@ -3993,7 +3993,7 @@
         <v>0.11200776661101834</v>
       </c>
       <c r="B358" s="0">
-        <v>0.032900597105841214</v>
+        <v>0.032900597105841215</v>
       </c>
       <c r="C358" s="0">
         <v>3.8546001453147483</v>
@@ -4018,7 +4018,7 @@
         <v>0.032273102615023183</v>
       </c>
       <c r="C360" s="0">
-        <v>3.7089690667050021</v>
+        <v>3.7089690667050022</v>
       </c>
     </row>
     <row r="361">
@@ -4026,7 +4026,7 @@
         <v>0.11294900834724539</v>
       </c>
       <c r="B361" s="0">
-        <v>0.031959355369614167</v>
+        <v>0.031959355369614168</v>
       </c>
       <c r="C361" s="0">
         <v>3.6372051329547186</v>
@@ -4040,7 +4040,7 @@
         <v>0.031645608124205138</v>
       </c>
       <c r="C362" s="0">
-        <v>3.5661422695741591</v>
+        <v>3.5661422695741592</v>
       </c>
     </row>
     <row r="363">
@@ -4389,7 +4389,7 @@
         <v>0.12330266744574289</v>
       </c>
       <c r="B394" s="0">
-        <v>0.021605696271116664</v>
+        <v>0.021605696271116665</v>
       </c>
       <c r="C394" s="0">
         <v>1.6622957966119527</v>
@@ -4425,7 +4425,7 @@
         <v>0.020667852944765606</v>
       </c>
       <c r="C397" s="0">
-        <v>1.5211165766901273</v>
+        <v>1.5211165766901274</v>
       </c>
     </row>
     <row r="398">
@@ -4535,7 +4535,7 @@
         <v>0.018391478244757703</v>
       </c>
       <c r="C407" s="0">
-        <v>1.2044951318913903</v>
+        <v>1.2044951318913904</v>
       </c>
     </row>
     <row r="408">
@@ -4579,7 +4579,7 @@
         <v>0.017802430869026852</v>
       </c>
       <c r="C411" s="0">
-        <v>1.1285749061820975</v>
+        <v>1.1285749061820976</v>
       </c>
     </row>
     <row r="412">
@@ -4752,7 +4752,7 @@
         <v>0.13365632654424037</v>
       </c>
       <c r="B427" s="0">
-        <v>0.016760475384550329</v>
+        <v>0.01676047538455033</v>
       </c>
       <c r="C427" s="0">
         <v>1.0003326376227799</v>
@@ -4851,7 +4851,7 @@
         <v>0.13648005175292152</v>
       </c>
       <c r="B436" s="0">
-        <v>0.016991012948391004</v>
+        <v>0.016991012948391005</v>
       </c>
       <c r="C436" s="0">
         <v>1.0280407156322902</v>
@@ -4876,7 +4876,7 @@
         <v>0.017122125604231205</v>
       </c>
       <c r="C438" s="0">
-        <v>1.04396786549075</v>
+        <v>1.0439678654907501</v>
       </c>
     </row>
     <row r="439">
@@ -5159,7 +5159,7 @@
         <v>0.14526497462437393</v>
       </c>
       <c r="B464" s="0">
-        <v>0.01908022928940627</v>
+        <v>0.019080229289406271</v>
       </c>
       <c r="C464" s="0">
         <v>1.2963997908657239</v>
@@ -5170,7 +5170,7 @@
         <v>0.14557872186978296</v>
       </c>
       <c r="B465" s="0">
-        <v>0.019155553338748878</v>
+        <v>0.019155553338748879</v>
       </c>
       <c r="C465" s="0">
         <v>1.306655729573365</v>
@@ -5211,7 +5211,7 @@
     </row>
     <row r="469">
       <c r="A469" s="0">
-        <v>0.14683371085141902</v>
+        <v>0.14683371085141903</v>
       </c>
       <c r="B469" s="0">
         <v>0.019456849536119283</v>
@@ -5250,7 +5250,7 @@
         <v>0.019682821684147079</v>
       </c>
       <c r="C472" s="0">
-        <v>1.3795787290393386</v>
+        <v>1.3795787290393387</v>
       </c>
     </row>
     <row r="473">
@@ -5335,7 +5335,7 @@
         <v>0.15028493055091818</v>
       </c>
       <c r="B480" s="0">
-        <v>0.020285414078887887</v>
+        <v>0.020285414078887888</v>
       </c>
       <c r="C480" s="0">
         <v>1.4653437895272288</v>
@@ -5343,10 +5343,10 @@
     </row>
     <row r="481">
       <c r="A481" s="0">
-        <v>0.15059867779632718</v>
+        <v>0.15059867779632719</v>
       </c>
       <c r="B481" s="0">
-        <v>0.020360738128230488</v>
+        <v>0.020360738128230489</v>
       </c>
       <c r="C481" s="0">
         <v>1.4762462588134375</v>
@@ -5354,7 +5354,7 @@
     </row>
     <row r="482">
       <c r="A482" s="0">
-        <v>0.15091242504173621</v>
+        <v>0.15091242504173622</v>
       </c>
       <c r="B482" s="0">
         <v>0.02043606217757309</v>
@@ -5365,7 +5365,7 @@
     </row>
     <row r="483">
       <c r="A483" s="0">
-        <v>0.15122617228714524</v>
+        <v>0.15122617228714525</v>
       </c>
       <c r="B483" s="0">
         <v>0.020511386226915698</v>
@@ -5437,7 +5437,7 @@
         <v>0.020963330522971297</v>
       </c>
       <c r="C489" s="0">
-        <v>1.564920706904886</v>
+        <v>1.5649207069048861</v>
       </c>
     </row>
     <row r="490">
@@ -5486,7 +5486,7 @@
     </row>
     <row r="494">
       <c r="A494" s="0">
-        <v>0.15467739198664437</v>
+        <v>0.15467739198664438</v>
       </c>
       <c r="B494" s="0">
         <v>0.021339950769684295</v>
@@ -5497,7 +5497,7 @@
     </row>
     <row r="495">
       <c r="A495" s="0">
-        <v>0.1549911392320534</v>
+        <v>0.15499113923205341</v>
       </c>
       <c r="B495" s="0">
         <v>0.021415274819026903</v>
@@ -5522,7 +5522,7 @@
         <v>0.15561863372287144</v>
       </c>
       <c r="B497" s="0">
-        <v>0.021565922917712105</v>
+        <v>0.021565922917712106</v>
       </c>
       <c r="C497" s="0">
         <v>1.6561812773106099</v>
@@ -5580,7 +5580,7 @@
         <v>0.021942543164425104</v>
       </c>
       <c r="C502" s="0">
-        <v>1.7145323990519032</v>
+        <v>1.7145323990519033</v>
       </c>
     </row>
     <row r="503">
@@ -5629,13 +5629,13 @@
     </row>
     <row r="507">
       <c r="A507" s="0">
-        <v>0.15875610617696156</v>
+        <v>0.15875610617696157</v>
       </c>
       <c r="B507" s="0">
         <v>0.022319163411138109</v>
       </c>
       <c r="C507" s="0">
-        <v>1.7738937248222117</v>
+        <v>1.7738937248222118</v>
       </c>
     </row>
     <row r="508">
@@ -5673,7 +5673,7 @@
     </row>
     <row r="511">
       <c r="A511" s="0">
-        <v>0.16001109515859765</v>
+        <v>0.16001109515859766</v>
       </c>
       <c r="B511" s="0">
         <v>0.02262045960850852</v>
@@ -5789,7 +5789,7 @@
         <v>0.023373700101934531</v>
       </c>
       <c r="C521" s="0">
-        <v>1.9454797224134281</v>
+        <v>1.9454797224134282</v>
       </c>
     </row>
     <row r="522">
@@ -5816,7 +5816,7 @@
     </row>
     <row r="524">
       <c r="A524" s="0">
-        <v>0.16408980934891484</v>
+        <v>0.16408980934891485</v>
       </c>
       <c r="B524" s="0">
         <v>0.023599672249962334</v>
@@ -5833,7 +5833,7 @@
         <v>0.023674996299304928</v>
       </c>
       <c r="C525" s="0">
-        <v>1.9959589869555538</v>
+        <v>1.9959589869555539</v>
       </c>
     </row>
     <row r="526">
@@ -5863,7 +5863,7 @@
         <v>0.16534479833055091</v>
       </c>
       <c r="B528" s="0">
-        <v>0.023900968447332738</v>
+        <v>0.023900968447332739</v>
       </c>
       <c r="C528" s="0">
         <v>2.0342427210543361</v>
@@ -5877,7 +5877,7 @@
         <v>0.023976292496675333</v>
       </c>
       <c r="C529" s="0">
-        <v>2.0470847820762494</v>
+        <v>2.0470847820762495</v>
       </c>
     </row>
     <row r="530">
@@ -5948,7 +5948,7 @@
     </row>
     <row r="536">
       <c r="A536" s="0">
-        <v>0.167854776293823</v>
+        <v>0.16785477629382301</v>
       </c>
       <c r="B536" s="0">
         <v>0.02450356084207354</v>
@@ -6039,7 +6039,7 @@
         <v>0.17036475425709513</v>
       </c>
       <c r="B544" s="0">
-        <v>0.025106153236814348</v>
+        <v>0.025106153236814349</v>
       </c>
       <c r="C544" s="0">
         <v>2.2445646767442344</v>
@@ -6185,7 +6185,7 @@
         <v>0.026085365878268162</v>
       </c>
       <c r="C557" s="0">
-        <v>2.4230682041210398</v>
+        <v>2.4230682041210399</v>
       </c>
     </row>
     <row r="558">
@@ -6196,7 +6196,7 @@
         <v>0.026160689927610763</v>
       </c>
       <c r="C558" s="0">
-        <v>2.4370821018166104</v>
+        <v>2.4370821018166105</v>
       </c>
     </row>
     <row r="559">
@@ -6369,7 +6369,7 @@
         <v>0.17977717161936557</v>
       </c>
       <c r="B574" s="0">
-        <v>0.027365874717092373</v>
+        <v>0.027365874717092374</v>
       </c>
       <c r="C574" s="0">
         <v>2.6667999748635687</v>
@@ -6380,7 +6380,7 @@
         <v>0.1800909188647746</v>
       </c>
       <c r="B575" s="0">
-        <v>0.027441198766434981</v>
+        <v>0.027441198766434982</v>
       </c>
       <c r="C575" s="0">
         <v>2.6815008112988692</v>
@@ -6391,7 +6391,7 @@
         <v>0.18040466611018363</v>
       </c>
       <c r="B576" s="0">
-        <v>0.027516522815777582</v>
+        <v>0.027516522815777583</v>
       </c>
       <c r="C576" s="0">
         <v>2.6962420558953291</v>
@@ -6460,7 +6460,7 @@
         <v>0.027968467111833182</v>
       </c>
       <c r="C582" s="0">
-        <v>2.78553809485846</v>
+        <v>2.7855380948584601</v>
       </c>
     </row>
     <row r="583">

--- a/REGEN/Contour_Maelstrom.xlsx
+++ b/REGEN/Contour_Maelstrom.xlsx
@@ -53,7 +53,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C600"/>
+  <dimension ref="A1:C620"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5546875" customWidth="true"/>
@@ -69,6596 +69,6816 @@
         <v>0.042227500000000001</v>
       </c>
       <c r="C1" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.00031374724540901501</v>
+        <v>0.00030361001615508883</v>
       </c>
       <c r="B2" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C2" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.00062749449081803003</v>
+        <v>0.00060722003231017765</v>
       </c>
       <c r="B3" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C3" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.00094124173622704504</v>
+        <v>0.00091083004846526647</v>
       </c>
       <c r="B4" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C4" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.00125498898163606</v>
+        <v>0.0012144400646203553</v>
       </c>
       <c r="B5" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C5" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.0015687362270450748</v>
+        <v>0.001518050080775444</v>
       </c>
       <c r="B6" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C6" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.0018824834724540901</v>
+        <v>0.0018216600969305329</v>
       </c>
       <c r="B7" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C7" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.0021962307178631049</v>
+        <v>0.0021252701130856219</v>
       </c>
       <c r="B8" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C8" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.0025099779632721201</v>
+        <v>0.0024288801292407106</v>
       </c>
       <c r="B9" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C9" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.0028237252086811349</v>
+        <v>0.0027324901453957993</v>
       </c>
       <c r="B10" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C10" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.0031374724540901497</v>
+        <v>0.003036100161550888</v>
       </c>
       <c r="B11" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C11" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.0034512196994991649</v>
+        <v>0.0033397101777059768</v>
       </c>
       <c r="B12" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C12" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.0037649669449081801</v>
+        <v>0.0036433201938610659</v>
       </c>
       <c r="B13" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C13" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.0040787141903171949</v>
+        <v>0.0039469302100161542</v>
       </c>
       <c r="B14" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C14" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.0043924614357262097</v>
+        <v>0.0042505402261712438</v>
       </c>
       <c r="B15" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C15" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>0.0047062086811352245</v>
+        <v>0.0045541502423263316</v>
       </c>
       <c r="B16" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C16" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>0.0050199559265442402</v>
+        <v>0.0048577602584814212</v>
       </c>
       <c r="B17" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C17" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.005333703171953255</v>
+        <v>0.0051613702746365099</v>
       </c>
       <c r="B18" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C18" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.0056474504173622698</v>
+        <v>0.0054649802907915986</v>
       </c>
       <c r="B19" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C19" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.0059611976627712855</v>
+        <v>0.0057685903069466882</v>
       </c>
       <c r="B20" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C20" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.0062749449081802994</v>
+        <v>0.0060722003231017761</v>
       </c>
       <c r="B21" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C21" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.006588692153589315</v>
+        <v>0.0063758103392568656</v>
       </c>
       <c r="B22" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C22" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.0069024393989983298</v>
+        <v>0.0066794203554119535</v>
       </c>
       <c r="B23" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C23" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>0.0072161866444073446</v>
+        <v>0.0069830303715670431</v>
       </c>
       <c r="B24" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C24" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>0.0075299338898163603</v>
+        <v>0.0072866403877221318</v>
       </c>
       <c r="B25" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C25" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>0.007843681135225376</v>
+        <v>0.0075902504038772214</v>
       </c>
       <c r="B26" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C26" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>0.0081574283806343899</v>
+        <v>0.0078938604200323084</v>
       </c>
       <c r="B27" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C27" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>0.0084711756260434038</v>
+        <v>0.0081974704361873988</v>
       </c>
       <c r="B28" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C28" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>0.0087849228714524195</v>
+        <v>0.0085010804523424875</v>
       </c>
       <c r="B29" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C29" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>0.0090986701168614351</v>
+        <v>0.0088046904684975762</v>
       </c>
       <c r="B30" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C30" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>0.0094124173622704491</v>
+        <v>0.0091083004846526632</v>
       </c>
       <c r="B31" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C31" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>0.0097261646076794647</v>
+        <v>0.0094119105008077537</v>
       </c>
       <c r="B32" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C32" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>0.01003991185308848</v>
+        <v>0.0097155205169628424</v>
       </c>
       <c r="B33" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C33" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>0.010353659098497494</v>
+        <v>0.010019130533117931</v>
       </c>
       <c r="B34" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C34" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>0.01066740634390651</v>
+        <v>0.01032274054927302</v>
       </c>
       <c r="B35" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C35" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>0.010981153589315524</v>
+        <v>0.010626350565428109</v>
       </c>
       <c r="B36" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C36" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>0.01129490083472454</v>
+        <v>0.010929960581583197</v>
       </c>
       <c r="B37" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C37" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>0.011608648080133555</v>
+        <v>0.011233570597738286</v>
       </c>
       <c r="B38" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C38" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>0.011922395325542571</v>
+        <v>0.011537180613893376</v>
       </c>
       <c r="B39" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C39" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>0.012236142570951583</v>
+        <v>0.011840790630048463</v>
       </c>
       <c r="B40" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C40" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>0.012549889816360599</v>
+        <v>0.012144400646203552</v>
       </c>
       <c r="B41" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C41" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>0.012863637061769614</v>
+        <v>0.012448010662358641</v>
       </c>
       <c r="B42" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C42" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>0.01317738430717863</v>
+        <v>0.012751620678513731</v>
       </c>
       <c r="B43" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C43" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>0.013491131552587644</v>
+        <v>0.013055230694668818</v>
       </c>
       <c r="B44" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C44" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>0.01380487879799666</v>
+        <v>0.013358840710823907</v>
       </c>
       <c r="B45" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C45" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>0.014118626043405674</v>
+        <v>0.013662450726978997</v>
       </c>
       <c r="B46" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C46" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>0.014432373288814689</v>
+        <v>0.013966060743134086</v>
       </c>
       <c r="B47" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C47" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>0.014746120534223705</v>
+        <v>0.014269670759289175</v>
       </c>
       <c r="B48" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C48" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>0.015059867779632721</v>
+        <v>0.014573280775444264</v>
       </c>
       <c r="B49" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C49" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>0.015373615025041736</v>
+        <v>0.014876890791599354</v>
       </c>
       <c r="B50" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C50" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>0.015687362270450752</v>
+        <v>0.015180500807754443</v>
       </c>
       <c r="B51" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C51" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>0.016001109515859764</v>
+        <v>0.015484110823909528</v>
       </c>
       <c r="B52" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C52" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>0.01631485676126878</v>
+        <v>0.015787720840064617</v>
       </c>
       <c r="B53" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C53" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>0.016628604006677795</v>
+        <v>0.016091330856219707</v>
       </c>
       <c r="B54" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C54" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>0.016942351252086808</v>
+        <v>0.016394940872374798</v>
       </c>
       <c r="B55" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C55" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>0.017256098497495823</v>
+        <v>0.016698550888529885</v>
       </c>
       <c r="B56" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C56" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>0.017569845742904839</v>
+        <v>0.017002160904684975</v>
       </c>
       <c r="B57" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C57" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>0.017883592988313855</v>
+        <v>0.017305770920840062</v>
       </c>
       <c r="B58" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C58" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>0.01819734023372287</v>
+        <v>0.017609380936995152</v>
       </c>
       <c r="B59" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C59" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>0.018511087479131886</v>
+        <v>0.017912990953150243</v>
       </c>
       <c r="B60" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C60" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>0.018824834724540898</v>
+        <v>0.018216600969305327</v>
       </c>
       <c r="B61" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C61" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>0.019138581969949914</v>
+        <v>0.018520210985460417</v>
       </c>
       <c r="B62" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C62" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>0.019452329215358929</v>
+        <v>0.018823821001615507</v>
       </c>
       <c r="B63" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C63" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>0.019766076460767945</v>
+        <v>0.019127431017770594</v>
       </c>
       <c r="B64" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C64" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>0.020079823706176961</v>
+        <v>0.019431041033925685</v>
       </c>
       <c r="B65" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C65" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>0.020393570951585977</v>
+        <v>0.019734651050080775</v>
       </c>
       <c r="B66" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C66" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.020707318196994989</v>
+        <v>0.020038261066235862</v>
       </c>
       <c r="B67" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C67" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.021021065442404004</v>
+        <v>0.020341871082390953</v>
       </c>
       <c r="B68" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C68" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.02133481268781302</v>
+        <v>0.02064548109854604</v>
       </c>
       <c r="B69" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C69" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.021648559933222032</v>
+        <v>0.020949091114701127</v>
       </c>
       <c r="B70" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C70" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.021962307178631048</v>
+        <v>0.021252701130856217</v>
       </c>
       <c r="B71" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C71" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.022276054424040064</v>
+        <v>0.021556311147011304</v>
       </c>
       <c r="B72" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C72" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.022589801669449079</v>
+        <v>0.021859921163166394</v>
       </c>
       <c r="B73" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C73" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.022903548914858095</v>
+        <v>0.022163531179321485</v>
       </c>
       <c r="B74" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C74" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.02321729616026711</v>
+        <v>0.022467141195476572</v>
       </c>
       <c r="B75" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C75" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.023531043405676126</v>
+        <v>0.022770751211631662</v>
       </c>
       <c r="B76" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C76" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.023844790651085142</v>
+        <v>0.023074361227786753</v>
       </c>
       <c r="B77" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C77" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.024158537896494154</v>
+        <v>0.02337797124394184</v>
       </c>
       <c r="B78" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C78" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.024472285141903166</v>
+        <v>0.023681581260096927</v>
       </c>
       <c r="B79" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C79" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.024786032387312182</v>
+        <v>0.023985191276252017</v>
       </c>
       <c r="B80" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C80" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.025099779632721197</v>
+        <v>0.024288801292407104</v>
       </c>
       <c r="B81" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C81" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.025413526878130213</v>
+        <v>0.024592411308562195</v>
       </c>
       <c r="B82" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C82" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.025727274123539229</v>
+        <v>0.024896021324717282</v>
       </c>
       <c r="B83" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C83" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.026041021368948244</v>
+        <v>0.025199631340872372</v>
       </c>
       <c r="B84" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C84" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.02635476861435726</v>
+        <v>0.025503241357027463</v>
       </c>
       <c r="B85" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C85" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.026668515859766276</v>
+        <v>0.02580685137318255</v>
       </c>
       <c r="B86" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C86" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.026982263105175288</v>
+        <v>0.026110461389337637</v>
       </c>
       <c r="B87" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C87" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.027296010350584307</v>
+        <v>0.02641407140549273</v>
       </c>
       <c r="B88" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C88" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.027609757595993319</v>
+        <v>0.026717681421647814</v>
       </c>
       <c r="B89" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C89" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.027923504841402335</v>
+        <v>0.027021291437802908</v>
       </c>
       <c r="B90" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C90" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0.028237252086811347</v>
+        <v>0.027324901453957995</v>
       </c>
       <c r="B91" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C91" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0.028550999332220366</v>
+        <v>0.027628511470113085</v>
       </c>
       <c r="B92" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C92" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0.028864746577629379</v>
+        <v>0.027932121486268172</v>
       </c>
       <c r="B93" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C93" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0.029178493823038391</v>
+        <v>0.028235731502423259</v>
       </c>
       <c r="B94" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C94" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0.02949224106844741</v>
+        <v>0.02853934151857835</v>
       </c>
       <c r="B95" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C95" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0.029805988313856422</v>
+        <v>0.028842951534733437</v>
       </c>
       <c r="B96" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C96" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0.030119735559265441</v>
+        <v>0.029146561550888527</v>
       </c>
       <c r="B97" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C97" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0.030433482804674453</v>
+        <v>0.029450171567043614</v>
       </c>
       <c r="B98" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C98" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0.030747230050083473</v>
+        <v>0.029753781583198708</v>
       </c>
       <c r="B99" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C99" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0.031060977295492485</v>
+        <v>0.030057391599353792</v>
       </c>
       <c r="B100" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C100" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="0">
-        <v>0.031374724540901504</v>
+        <v>0.030361001615508885</v>
       </c>
       <c r="B101" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C101" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="0">
-        <v>0.031688471786310513</v>
+        <v>0.030664611631663973</v>
       </c>
       <c r="B102" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C102" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="0">
-        <v>0.032002219031719528</v>
+        <v>0.030968221647819056</v>
       </c>
       <c r="B103" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C103" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="0">
-        <v>0.032315966277128544</v>
+        <v>0.031271831663974146</v>
       </c>
       <c r="B104" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C104" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="0">
-        <v>0.03262971352253756</v>
+        <v>0.031575441680129234</v>
       </c>
       <c r="B105" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C105" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="0">
-        <v>0.032943460767946575</v>
+        <v>0.031879051696284327</v>
       </c>
       <c r="B106" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C106" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="0">
-        <v>0.033257208013355591</v>
+        <v>0.032182661712439414</v>
       </c>
       <c r="B107" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C107" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="0">
-        <v>0.033570955258764607</v>
+        <v>0.032486271728594508</v>
       </c>
       <c r="B108" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C108" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="0">
-        <v>0.033884702504173615</v>
+        <v>0.032789881744749595</v>
       </c>
       <c r="B109" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C109" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="0">
-        <v>0.034198449749582638</v>
+        <v>0.033093491760904682</v>
       </c>
       <c r="B110" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C110" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="0">
-        <v>0.034512196994991647</v>
+        <v>0.033397101777059769</v>
       </c>
       <c r="B111" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C111" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="0">
-        <v>0.034825944240400662</v>
+        <v>0.033700711793214856</v>
       </c>
       <c r="B112" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C112" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="0">
-        <v>0.035139691485809678</v>
+        <v>0.03400432180936995</v>
       </c>
       <c r="B113" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C113" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="0">
-        <v>0.035453438731218694</v>
+        <v>0.034307931825525037</v>
       </c>
       <c r="B114" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C114" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="0">
-        <v>0.035767185976627709</v>
+        <v>0.034611541841680124</v>
       </c>
       <c r="B115" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C115" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="0">
-        <v>0.036080933222036725</v>
+        <v>0.034915151857835211</v>
       </c>
       <c r="B116" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C116" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="0">
-        <v>0.036394680467445741</v>
+        <v>0.035218761873990305</v>
       </c>
       <c r="B117" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C117" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="0">
-        <v>0.036708427712854756</v>
+        <v>0.035522371890145392</v>
       </c>
       <c r="B118" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C118" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="0">
-        <v>0.037022174958263772</v>
+        <v>0.035825981906300486</v>
       </c>
       <c r="B119" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C119" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="0">
-        <v>0.037335922203672781</v>
+        <v>0.036129591922455573</v>
       </c>
       <c r="B120" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C120" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="0">
-        <v>0.037649669449081796</v>
+        <v>0.036433201938610653</v>
       </c>
       <c r="B121" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C121" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="0">
-        <v>0.037963416694490812</v>
+        <v>0.036736811954765747</v>
       </c>
       <c r="B122" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C122" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="0">
-        <v>0.038277163939899828</v>
+        <v>0.037040421970920834</v>
       </c>
       <c r="B123" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C123" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="0">
-        <v>0.038590911185308843</v>
+        <v>0.037344031987075928</v>
       </c>
       <c r="B124" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C124" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="0">
-        <v>0.038904658430717859</v>
+        <v>0.037647642003231015</v>
       </c>
       <c r="B125" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C125" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="0">
-        <v>0.039218405676126875</v>
+        <v>0.037951252019386102</v>
       </c>
       <c r="B126" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C126" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="0">
-        <v>0.03953215292153589</v>
+        <v>0.038254862035541189</v>
       </c>
       <c r="B127" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C127" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="0">
-        <v>0.039845900166944906</v>
+        <v>0.038558472051696283</v>
       </c>
       <c r="B128" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C128" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="0">
-        <v>0.040159647412353922</v>
+        <v>0.03886208206785137</v>
       </c>
       <c r="B129" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C129" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="0">
-        <v>0.04047339465776293</v>
+        <v>0.039165692084006457</v>
       </c>
       <c r="B130" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C130" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="0">
-        <v>0.040787141903171953</v>
+        <v>0.03946930210016155</v>
       </c>
       <c r="B131" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C131" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="0">
-        <v>0.041100889148580962</v>
+        <v>0.039772912116316631</v>
       </c>
       <c r="B132" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C132" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="0">
-        <v>0.041414636393989977</v>
+        <v>0.040076522132471725</v>
       </c>
       <c r="B133" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C133" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="0">
-        <v>0.041728383639398993</v>
+        <v>0.040380132148626811</v>
       </c>
       <c r="B134" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C134" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="0">
-        <v>0.042042130884808009</v>
+        <v>0.040683742164781905</v>
       </c>
       <c r="B135" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C135" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="0">
-        <v>0.042355878130217024</v>
+        <v>0.040987352180936992</v>
       </c>
       <c r="B136" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C136" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="0">
-        <v>0.04266962537562604</v>
+        <v>0.041290962197092079</v>
       </c>
       <c r="B137" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C137" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="0">
-        <v>0.042983372621035056</v>
+        <v>0.041594572213247166</v>
       </c>
       <c r="B138" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C138" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="0">
-        <v>0.043297119866444064</v>
+        <v>0.041898182229402253</v>
       </c>
       <c r="B139" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C139" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="0">
-        <v>0.043610867111853087</v>
+        <v>0.042201792245557347</v>
       </c>
       <c r="B140" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C140" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="0">
-        <v>0.043924614357262096</v>
+        <v>0.042505402261712434</v>
       </c>
       <c r="B141" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C141" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="0">
-        <v>0.044238361602671118</v>
+        <v>0.042809012277867528</v>
       </c>
       <c r="B142" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C142" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="0">
-        <v>0.044552108848080127</v>
+        <v>0.043112622294022608</v>
       </c>
       <c r="B143" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C143" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="0">
-        <v>0.044865856093489143</v>
+        <v>0.043416232310177702</v>
       </c>
       <c r="B144" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C144" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="0">
-        <v>0.045179603338898158</v>
+        <v>0.043719842326332789</v>
       </c>
       <c r="B145" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C145" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="0">
-        <v>0.045493350584307174</v>
+        <v>0.044023452342487883</v>
       </c>
       <c r="B146" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C146" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="0">
-        <v>0.04580709782971619</v>
+        <v>0.04432706235864297</v>
       </c>
       <c r="B147" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C147" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="0">
-        <v>0.046120845075125198</v>
+        <v>0.044630672374798057</v>
       </c>
       <c r="B148" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C148" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="0">
-        <v>0.046434592320534221</v>
+        <v>0.044934282390953144</v>
       </c>
       <c r="B149" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C149" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="0">
-        <v>0.04674833956594323</v>
+        <v>0.045237892407108231</v>
       </c>
       <c r="B150" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C150" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="0">
-        <v>0.047062086811352252</v>
+        <v>0.045541502423263325</v>
       </c>
       <c r="B151" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C151" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="0">
-        <v>0.047375834056761261</v>
+        <v>0.045845112439418412</v>
       </c>
       <c r="B152" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C152" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="0">
-        <v>0.047689581302170284</v>
+        <v>0.046148722455573506</v>
       </c>
       <c r="B153" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C153" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="0">
-        <v>0.048003328547579292</v>
+        <v>0.046452332471728586</v>
       </c>
       <c r="B154" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C154" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="0">
-        <v>0.048317075792988308</v>
+        <v>0.04675594248788368</v>
       </c>
       <c r="B155" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C155" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="0">
-        <v>0.048630823038397324</v>
+        <v>0.047059552504038767</v>
       </c>
       <c r="B156" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C156" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="0">
-        <v>0.048944570283806332</v>
+        <v>0.047363162520193854</v>
       </c>
       <c r="B157" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C157" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="0">
-        <v>0.049258317529215355</v>
+        <v>0.047666772536348948</v>
       </c>
       <c r="B158" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C158" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="0">
-        <v>0.049572064774624364</v>
+        <v>0.047970382552504034</v>
       </c>
       <c r="B159" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C159" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="0">
-        <v>0.049885812020033386</v>
+        <v>0.048273992568659122</v>
       </c>
       <c r="B160" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C160" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="0">
-        <v>0.050199559265442395</v>
+        <v>0.048577602584814208</v>
       </c>
       <c r="B161" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C161" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="0">
-        <v>0.050513306510851418</v>
+        <v>0.048881212600969302</v>
       </c>
       <c r="B162" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C162" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="0">
-        <v>0.050827053756260426</v>
+        <v>0.049184822617124389</v>
       </c>
       <c r="B163" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C163" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="0">
-        <v>0.051140801001669449</v>
+        <v>0.049488432633279483</v>
       </c>
       <c r="B164" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C164" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="0">
-        <v>0.051454548247078458</v>
+        <v>0.049792042649434563</v>
       </c>
       <c r="B165" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C165" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="0">
-        <v>0.051768295492487473</v>
+        <v>0.05009565266558965</v>
       </c>
       <c r="B166" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C166" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="0">
-        <v>0.052082042737896489</v>
+        <v>0.050399262681744744</v>
       </c>
       <c r="B167" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C167" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="0">
-        <v>0.052395789983305505</v>
+        <v>0.050702872697899831</v>
       </c>
       <c r="B168" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C168" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="0">
-        <v>0.05270953722871452</v>
+        <v>0.051006482714054925</v>
       </c>
       <c r="B169" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C169" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="0">
-        <v>0.053023284474123529</v>
+        <v>0.051310092730210012</v>
       </c>
       <c r="B170" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C170" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="0">
-        <v>0.053337031719532552</v>
+        <v>0.051613702746365099</v>
       </c>
       <c r="B171" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C171" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="0">
-        <v>0.05365077896494156</v>
+        <v>0.051917312762520186</v>
       </c>
       <c r="B172" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C172" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="0">
-        <v>0.053964526210350576</v>
+        <v>0.052220922778675273</v>
       </c>
       <c r="B173" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C173" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="0">
-        <v>0.054278273455759599</v>
+        <v>0.052524532794830374</v>
       </c>
       <c r="B174" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C174" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="0">
-        <v>0.054592020701168614</v>
+        <v>0.052828142810985461</v>
       </c>
       <c r="B175" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C175" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="0">
-        <v>0.054905767946577623</v>
+        <v>0.053131752827140541</v>
       </c>
       <c r="B176" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C176" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="0">
-        <v>0.055219515191986639</v>
+        <v>0.053435362843295628</v>
       </c>
       <c r="B177" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C177" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="0">
-        <v>0.055533262437395647</v>
+        <v>0.053738972859450715</v>
       </c>
       <c r="B178" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C178" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="0">
-        <v>0.05584700968280467</v>
+        <v>0.054042582875605816</v>
       </c>
       <c r="B179" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C179" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="0">
-        <v>0.056160756928213686</v>
+        <v>0.054346192891760903</v>
       </c>
       <c r="B180" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C180" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="0">
-        <v>0.056474504173622694</v>
+        <v>0.05464980290791599</v>
       </c>
       <c r="B181" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C181" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="0">
-        <v>0.05678825141903171</v>
+        <v>0.05495341292407107</v>
       </c>
       <c r="B182" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C182" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="0">
-        <v>0.057101998664440733</v>
+        <v>0.055257022940226171</v>
       </c>
       <c r="B183" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C183" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="0">
-        <v>0.057415745909849748</v>
+        <v>0.055560632956381258</v>
       </c>
       <c r="B184" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C184" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="0">
-        <v>0.057729493155258757</v>
+        <v>0.055864242972536345</v>
       </c>
       <c r="B185" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C185" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="0">
-        <v>0.058043240400667773</v>
+        <v>0.056167852988691432</v>
       </c>
       <c r="B186" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C186" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="0">
-        <v>0.058356987646076782</v>
+        <v>0.056471463004846519</v>
       </c>
       <c r="B187" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C187" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="0">
-        <v>0.058670734891485811</v>
+        <v>0.056775073021001613</v>
       </c>
       <c r="B188" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C188" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="0">
-        <v>0.05898448213689482</v>
+        <v>0.057078683037156699</v>
       </c>
       <c r="B189" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C189" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="0">
-        <v>0.059298229382303835</v>
+        <v>0.057382293053311787</v>
       </c>
       <c r="B190" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C190" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="0">
-        <v>0.059611976627712844</v>
+        <v>0.057685903069466873</v>
       </c>
       <c r="B191" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C191" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="0">
-        <v>0.059925723873121867</v>
+        <v>0.057989513085621967</v>
       </c>
       <c r="B192" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C192" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="0">
-        <v>0.060239471118530882</v>
+        <v>0.058293123101777054</v>
       </c>
       <c r="B193" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C193" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="0">
-        <v>0.060553218363939891</v>
+        <v>0.058596733117932141</v>
       </c>
       <c r="B194" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C194" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="0">
-        <v>0.060866965609348907</v>
+        <v>0.058900343134087228</v>
       </c>
       <c r="B195" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C195" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="0">
-        <v>0.061180712854757915</v>
+        <v>0.059203953150242315</v>
       </c>
       <c r="B196" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C196" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="0">
-        <v>0.061494460100166945</v>
+        <v>0.059507563166397416</v>
       </c>
       <c r="B197" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C197" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="0">
-        <v>0.061808207345575954</v>
+        <v>0.059811173182552496</v>
       </c>
       <c r="B198" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C198" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="0">
-        <v>0.062121954590984969</v>
+        <v>0.060114783198707583</v>
       </c>
       <c r="B199" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C199" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="0">
-        <v>0.062435701836393978</v>
+        <v>0.06041839321486267</v>
       </c>
       <c r="B200" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C200" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="0">
-        <v>0.062749449081803008</v>
+        <v>0.060722003231017771</v>
       </c>
       <c r="B201" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C201" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="0">
-        <v>0.063063196327212009</v>
+        <v>0.061025613247172858</v>
       </c>
       <c r="B202" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C202" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="0">
-        <v>0.063376943572621025</v>
+        <v>0.061329223263327945</v>
       </c>
       <c r="B203" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C203" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="0">
-        <v>0.063690690818030041</v>
+        <v>0.061632833279483025</v>
       </c>
       <c r="B204" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C204" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="0">
-        <v>0.064004438063439056</v>
+        <v>0.061936443295638112</v>
       </c>
       <c r="B205" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C205" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="0">
-        <v>0.064318185308848072</v>
+        <v>0.062240053311793213</v>
       </c>
       <c r="B206" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C206" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="0">
-        <v>0.064631932554257088</v>
+        <v>0.062543663327948293</v>
       </c>
       <c r="B207" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C207" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="0">
-        <v>0.064945679799666103</v>
+        <v>0.06284727334410338</v>
       </c>
       <c r="B208" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C208" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="0">
-        <v>0.065259427045075119</v>
+        <v>0.063150883360258467</v>
       </c>
       <c r="B209" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C209" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="0">
-        <v>0.065573174290484135</v>
+        <v>0.063454493376413568</v>
       </c>
       <c r="B210" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C210" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="0">
-        <v>0.06588692153589315</v>
+        <v>0.063758103392568655</v>
       </c>
       <c r="B211" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C211" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="0">
-        <v>0.066200668781302166</v>
+        <v>0.064061713408723742</v>
       </c>
       <c r="B212" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C212" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="0">
-        <v>0.066514416026711182</v>
+        <v>0.064365323424878829</v>
       </c>
       <c r="B213" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C213" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="0">
-        <v>0.066828163272120183</v>
+        <v>0.064668933441033916</v>
       </c>
       <c r="B214" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C214" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="0">
-        <v>0.067141910517529213</v>
+        <v>0.064972543457189017</v>
       </c>
       <c r="B215" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C215" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="0">
-        <v>0.067455657762938229</v>
+        <v>0.065276153473344103</v>
       </c>
       <c r="B216" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C216" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="0">
-        <v>0.06776940500834723</v>
+        <v>0.06557976348949919</v>
       </c>
       <c r="B217" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C217" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="0">
-        <v>0.068083152253756246</v>
+        <v>0.065883373505654264</v>
       </c>
       <c r="B218" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C218" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="0">
-        <v>0.068396899499165276</v>
+        <v>0.066186983521809364</v>
       </c>
       <c r="B219" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C219" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="0">
-        <v>0.068710646744574291</v>
+        <v>0.066490593537964451</v>
       </c>
       <c r="B220" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C220" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="0">
-        <v>0.069024393989983293</v>
+        <v>0.066794203554119538</v>
       </c>
       <c r="B221" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C221" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="0">
-        <v>0.069338141235392309</v>
+        <v>0.067097813570274625</v>
       </c>
       <c r="B222" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C222" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="0">
-        <v>0.069651888480801324</v>
+        <v>0.067401423586429712</v>
       </c>
       <c r="B223" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C223" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="0">
-        <v>0.069965635726210354</v>
+        <v>0.067705033602584813</v>
       </c>
       <c r="B224" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C224" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="0">
-        <v>0.070279382971619356</v>
+        <v>0.0680086436187399</v>
       </c>
       <c r="B225" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C225" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="0">
-        <v>0.070593130217028372</v>
+        <v>0.068312253634894987</v>
       </c>
       <c r="B226" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C226" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="0">
-        <v>0.070906877462437387</v>
+        <v>0.068615863651050074</v>
       </c>
       <c r="B227" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C227" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="0">
-        <v>0.071220624707846403</v>
+        <v>0.068919473667205161</v>
       </c>
       <c r="B228" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C228" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="0">
-        <v>0.071534371953255419</v>
+        <v>0.069223083683360248</v>
       </c>
       <c r="B229" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C229" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="0">
-        <v>0.071848119198664434</v>
+        <v>0.069526693699515335</v>
       </c>
       <c r="B230" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C230" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="0">
-        <v>0.07216186644407345</v>
+        <v>0.069830303715670422</v>
       </c>
       <c r="B231" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C231" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="0">
-        <v>0.072475613689482452</v>
+        <v>0.070133913731825509</v>
       </c>
       <c r="B232" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C232" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="0">
-        <v>0.072789360934891481</v>
+        <v>0.07043752374798061</v>
       </c>
       <c r="B233" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C233" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="0">
-        <v>0.073103108180300497</v>
+        <v>0.070741133764135697</v>
       </c>
       <c r="B234" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C234" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="0">
-        <v>0.073416855425709512</v>
+        <v>0.071044743780290784</v>
       </c>
       <c r="B235" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C235" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="0">
-        <v>0.073730602671118514</v>
+        <v>0.071348353796445871</v>
       </c>
       <c r="B236" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C236" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="0">
-        <v>0.074044349916527544</v>
+        <v>0.071651963812600972</v>
       </c>
       <c r="B237" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C237" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="0">
-        <v>0.074358097161936559</v>
+        <v>0.071955573828756059</v>
       </c>
       <c r="B238" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C238" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="0">
-        <v>0.074671844407345561</v>
+        <v>0.072259183844911146</v>
       </c>
       <c r="B239" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C239" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="0">
-        <v>0.074985591652754577</v>
+        <v>0.072562793861066219</v>
       </c>
       <c r="B240" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C240" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="0">
-        <v>0.075299338898163593</v>
+        <v>0.072866403877221306</v>
       </c>
       <c r="B241" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C241" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="0">
-        <v>0.075613086143572622</v>
+        <v>0.073170013893376407</v>
       </c>
       <c r="B242" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C242" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="0">
-        <v>0.075926833388981624</v>
+        <v>0.073473623909531494</v>
       </c>
       <c r="B243" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C243" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="0">
-        <v>0.07624058063439064</v>
+        <v>0.073777233925686581</v>
       </c>
       <c r="B244" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C244" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="0">
-        <v>0.076554327879799655</v>
+        <v>0.074080843941841668</v>
       </c>
       <c r="B245" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C245" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="0">
-        <v>0.076868075125208685</v>
+        <v>0.074384453957996769</v>
       </c>
       <c r="B246" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C246" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="0">
-        <v>0.077181822370617687</v>
+        <v>0.074688063974151855</v>
       </c>
       <c r="B247" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C247" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="0">
-        <v>0.077495569616026702</v>
+        <v>0.074991673990306942</v>
       </c>
       <c r="B248" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C248" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="0">
-        <v>0.077809316861435718</v>
+        <v>0.075295284006462029</v>
       </c>
       <c r="B249" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C249" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="0">
-        <v>0.078123064106844734</v>
+        <v>0.075598894022617116</v>
       </c>
       <c r="B250" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C250" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="0">
-        <v>0.078436811352253749</v>
+        <v>0.075902504038772203</v>
       </c>
       <c r="B251" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C251" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="0">
-        <v>0.078750558597662765</v>
+        <v>0.07620611405492729</v>
       </c>
       <c r="B252" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C252" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="0">
-        <v>0.079064305843071781</v>
+        <v>0.076509724071082377</v>
       </c>
       <c r="B253" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C253" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="0">
-        <v>0.079378053088480782</v>
+        <v>0.076813334087237464</v>
       </c>
       <c r="B254" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C254" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="0">
-        <v>0.079691800333889812</v>
+        <v>0.077116944103392565</v>
       </c>
       <c r="B255" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C255" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="0">
-        <v>0.080005547579298828</v>
+        <v>0.077420554119547652</v>
       </c>
       <c r="B256" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C256" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="0">
-        <v>0.080319294824707843</v>
+        <v>0.077724164135702739</v>
       </c>
       <c r="B257" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C257" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="0">
-        <v>0.080633042070116845</v>
+        <v>0.078027774151857826</v>
       </c>
       <c r="B258" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C258" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="0">
-        <v>0.080946789315525861</v>
+        <v>0.078331384168012913</v>
       </c>
       <c r="B259" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C259" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="0">
-        <v>0.08126053656093489</v>
+        <v>0.078634994184168014</v>
       </c>
       <c r="B260" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C260" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="0">
-        <v>0.081574283806343906</v>
+        <v>0.078938604200323101</v>
       </c>
       <c r="B261" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C261" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="0">
-        <v>0.081888031051752908</v>
+        <v>0.079242214216478174</v>
       </c>
       <c r="B262" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C262" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="0">
-        <v>0.082201778297161923</v>
+        <v>0.079545824232633261</v>
       </c>
       <c r="B263" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C263" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="0">
-        <v>0.082515525542570953</v>
+        <v>0.079849434248788362</v>
       </c>
       <c r="B264" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C264" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="0">
-        <v>0.082829272787979955</v>
+        <v>0.080153044264943449</v>
       </c>
       <c r="B265" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C265" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="0">
-        <v>0.08314302003338897</v>
+        <v>0.080456654281098536</v>
       </c>
       <c r="B266" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C266" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="0">
-        <v>0.083456767278797986</v>
+        <v>0.080760264297253623</v>
       </c>
       <c r="B267" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C267" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="0">
-        <v>0.083770514524207002</v>
+        <v>0.08106387431340871</v>
       </c>
       <c r="B268" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C268" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="0">
-        <v>0.084084261769616017</v>
+        <v>0.081367484329563811</v>
       </c>
       <c r="B269" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C269" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="0">
-        <v>0.084398009015025033</v>
+        <v>0.081671094345718898</v>
       </c>
       <c r="B270" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C270" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="0">
-        <v>0.084711756260434048</v>
+        <v>0.081974704361873985</v>
       </c>
       <c r="B271" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C271" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="0">
-        <v>0.085025503505843064</v>
+        <v>0.082278314378029072</v>
       </c>
       <c r="B272" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C272" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="0">
-        <v>0.08533925075125208</v>
+        <v>0.082581924394184159</v>
       </c>
       <c r="B273" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C273" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="0">
-        <v>0.085652997996661095</v>
+        <v>0.082885534410339246</v>
       </c>
       <c r="B274" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C274" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="0">
-        <v>0.085966745242070111</v>
+        <v>0.083189144426494333</v>
       </c>
       <c r="B275" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C275" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="0">
-        <v>0.086280492487479113</v>
+        <v>0.08349275444264942</v>
       </c>
       <c r="B276" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C276" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="0">
-        <v>0.086594239732888129</v>
+        <v>0.083796364458804506</v>
       </c>
       <c r="B277" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C277" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="0">
-        <v>0.086907986978297158</v>
+        <v>0.084099974474959607</v>
       </c>
       <c r="B278" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C278" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="0">
-        <v>0.087221734223706174</v>
+        <v>0.084403584491114694</v>
       </c>
       <c r="B279" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C279" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="0">
-        <v>0.087535481469115176</v>
+        <v>0.084707194507269781</v>
       </c>
       <c r="B280" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C280" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="0">
-        <v>0.087849228714524191</v>
+        <v>0.085010804523424868</v>
       </c>
       <c r="B281" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C281" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="0">
-        <v>0.088162975959933221</v>
+        <v>0.085314414539579969</v>
       </c>
       <c r="B282" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C282" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="0">
-        <v>0.088476723205342236</v>
+        <v>0.085618024555735056</v>
       </c>
       <c r="B283" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C283" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="0">
-        <v>0.088790470450751238</v>
+        <v>0.085921634571890129</v>
       </c>
       <c r="B284" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C284" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="0">
-        <v>0.089104217696160254</v>
+        <v>0.086225244588045216</v>
       </c>
       <c r="B285" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C285" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="0">
-        <v>0.08941796494156927</v>
+        <v>0.086528854604200303</v>
       </c>
       <c r="B286" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C286" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="0">
-        <v>0.089731712186978285</v>
+        <v>0.086832464620355404</v>
       </c>
       <c r="B287" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C287" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="0">
-        <v>0.090045459432387301</v>
+        <v>0.087136074636510491</v>
       </c>
       <c r="B288" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C288" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="0">
-        <v>0.090359206677796317</v>
+        <v>0.087439684652665578</v>
       </c>
       <c r="B289" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C289" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="0">
-        <v>0.090672953923205332</v>
+        <v>0.087743294668820665</v>
       </c>
       <c r="B290" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C290" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="0">
-        <v>0.090986701168614348</v>
+        <v>0.088046904684975766</v>
       </c>
       <c r="B291" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C291" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="0">
-        <v>0.091300448414023364</v>
+        <v>0.088350514701130853</v>
       </c>
       <c r="B292" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C292" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="0">
-        <v>0.091614195659432379</v>
+        <v>0.08865412471728594</v>
       </c>
       <c r="B293" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C293" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="0">
-        <v>0.091927942904841395</v>
+        <v>0.088957734733441027</v>
       </c>
       <c r="B294" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C294" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="0">
-        <v>0.092241690150250397</v>
+        <v>0.089261344749596114</v>
       </c>
       <c r="B295" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C295" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="0">
-        <v>0.092555437395659426</v>
+        <v>0.089564954765751201</v>
       </c>
       <c r="B296" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C296" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="0">
-        <v>0.092869184641068442</v>
+        <v>0.089868564781906288</v>
       </c>
       <c r="B297" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C297" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="0">
-        <v>0.093182931886477458</v>
+        <v>0.090172174798061375</v>
       </c>
       <c r="B298" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C298" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="0">
-        <v>0.093496679131886459</v>
+        <v>0.090475784814216462</v>
       </c>
       <c r="B299" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C299" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="0">
-        <v>0.093810426377295489</v>
+        <v>0.090779394830371563</v>
       </c>
       <c r="B300" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C300" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="0">
-        <v>0.094124173622704504</v>
+        <v>0.09108300484652665</v>
       </c>
       <c r="B301" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C301" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="0">
-        <v>0.094437920868113506</v>
+        <v>0.091386614862681737</v>
       </c>
       <c r="B302" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C302" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="0">
-        <v>0.094751668113522522</v>
+        <v>0.091690224878836824</v>
       </c>
       <c r="B303" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C303" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="0">
-        <v>0.095065415358931538</v>
+        <v>0.09199383489499191</v>
       </c>
       <c r="B304" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C304" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="0">
-        <v>0.095379162604340567</v>
+        <v>0.092297444911147011</v>
       </c>
       <c r="B305" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C305" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="0">
-        <v>0.095692909849749569</v>
+        <v>0.092601054927302084</v>
       </c>
       <c r="B306" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C306" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="0">
-        <v>0.096006657095158585</v>
+        <v>0.092904664943457172</v>
       </c>
       <c r="B307" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C307" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="0">
-        <v>0.0963204043405676</v>
+        <v>0.093208274959612258</v>
       </c>
       <c r="B308" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C308" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="0">
-        <v>0.096634151585976616</v>
+        <v>0.093511884975767359</v>
       </c>
       <c r="B309" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C309" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="0">
-        <v>0.096947898831385632</v>
+        <v>0.093815494991922446</v>
       </c>
       <c r="B310" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C310" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="0">
-        <v>0.097261646076794647</v>
+        <v>0.094119105008077533</v>
       </c>
       <c r="B311" s="0">
         <v>0.042227500000000001</v>
       </c>
       <c r="C311" s="0">
-        <v>6.3498360881767546</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="0">
-        <v>0.097575393322203663</v>
+        <v>0.09442271502423262</v>
       </c>
       <c r="B312" s="0">
-        <v>0.042226553587788707</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C312" s="0">
-        <v>6.3495514634620651</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="0">
-        <v>0.097889140567612665</v>
+        <v>0.094726325040387707</v>
       </c>
       <c r="B313" s="0">
-        <v>0.042218844955771474</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C313" s="0">
-        <v>6.3472334013012652</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="0">
-        <v>0.098202887813021694</v>
+        <v>0.095029935056542808</v>
       </c>
       <c r="B314" s="0">
-        <v>0.042203368288967008</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C314" s="0">
-        <v>6.3425806917742254</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="0">
-        <v>0.09851663505843071</v>
+        <v>0.095333545072697895</v>
       </c>
       <c r="B315" s="0">
-        <v>0.04218009508180394</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C315" s="0">
-        <v>6.3355873403087175</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="0">
-        <v>0.098830382303839726</v>
+        <v>0.095637155088852982</v>
       </c>
       <c r="B316" s="0">
-        <v>0.042148982205388382</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C316" s="0">
-        <v>6.3262442771244309</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="0">
-        <v>0.099144129549248727</v>
+        <v>0.095940765105008069</v>
       </c>
       <c r="B317" s="0">
-        <v>0.042109971504032041</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C317" s="0">
-        <v>6.3145392723849634</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="0">
-        <v>0.099457876794657757</v>
+        <v>0.096244375121163156</v>
       </c>
       <c r="B318" s="0">
-        <v>0.04206298924336891</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C318" s="0">
-        <v>6.3004568201396527</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="0">
-        <v>0.099771624040066773</v>
+        <v>0.096547985137318243</v>
       </c>
       <c r="B319" s="0">
-        <v>0.042007945397639204</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C319" s="0">
-        <v>6.283977988443124</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="0">
-        <v>0.10008537128547579</v>
+        <v>0.09685159515347333</v>
       </c>
       <c r="B320" s="0">
-        <v>0.041944732759688685</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C320" s="0">
-        <v>6.2650802321928048</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="0">
-        <v>0.10039911853088479</v>
+        <v>0.097155205169628417</v>
       </c>
       <c r="B321" s="0">
-        <v>0.041873225852501132</v>
+        <v>0.042227500000000001</v>
       </c>
       <c r="C321" s="0">
-        <v>6.243737164229926</v>
+        <v>6.3498097005257286</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="0">
-        <v>0.10071286577629381</v>
+        <v>0.097458815185783504</v>
       </c>
       <c r="B322" s="0">
-        <v>0.041793279615415416</v>
+        <v>0.04222744175352515</v>
       </c>
       <c r="C322" s="0">
-        <v>6.2199182790578407</v>
+        <v>6.3497921833259925</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="0">
-        <v>0.10102661302170284</v>
+        <v>0.097762425201938605</v>
       </c>
       <c r="B323" s="0">
-        <v>0.041704727831274324</v>
+        <v>0.042222892296622724</v>
       </c>
       <c r="C323" s="0">
-        <v>6.1935886220796856</v>
+        <v>6.3484240422064131</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="0">
-        <v>0.10134036026711184</v>
+        <v>0.098066035218093692</v>
       </c>
       <c r="B324" s="0">
-        <v>0.041607381252213555</v>
+        <v>0.0422110756986563</v>
       </c>
       <c r="C324" s="0">
-        <v>6.1647083954616138</v>
+        <v>6.3448711696597053</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="0">
-        <v>0.10165410751252085</v>
+        <v>0.098369645234248779</v>
       </c>
       <c r="B325" s="0">
-        <v>0.041501025371100841</v>
+        <v>0.042191971617802387</v>
       </c>
       <c r="C325" s="0">
-        <v>6.1332324894781367</v>
+        <v>6.3391292879247949</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="0">
-        <v>0.10196785475792987</v>
+        <v>0.098673255250403866</v>
       </c>
       <c r="B326" s="0">
-        <v>0.041385417772071408</v>
+        <v>0.04216554700611927</v>
       </c>
       <c r="C326" s="0">
-        <v>6.0991099253436056</v>
+        <v>6.3311914472216531</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="0">
-        <v>0.1022816020033389</v>
+        <v>0.098976865266558967</v>
       </c>
       <c r="B327" s="0">
-        <v>0.041260284976211516</v>
+        <v>0.042131755821579436</v>
       </c>
       <c r="C327" s="0">
-        <v>6.0622831918760127</v>
+        <v>6.3210479651934817</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="0">
-        <v>0.1025953492487479</v>
+        <v>0.09928047528271404</v>
       </c>
       <c r="B328" s="0">
-        <v>0.041125318675889845</v>
+        <v>0.042090538622042775</v>
       </c>
       <c r="C328" s="0">
-        <v>6.0226874535966113</v>
+        <v>6.3086863415217467</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="0">
-        <v>0.10290909649415692</v>
+        <v>0.099584085298869127</v>
       </c>
       <c r="B329" s="0">
-        <v>0.040980171221667902</v>
+        <v>0.042041822032704707</v>
       </c>
       <c r="C329" s="0">
-        <v>5.9802496016508266</v>
+        <v>6.2940911459337947</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="0">
-        <v>0.10322284373956593</v>
+        <v>0.099887695315024214</v>
       </c>
       <c r="B330" s="0">
-        <v>0.040824450186506878</v>
+        <v>0.041985518075669942</v>
       </c>
       <c r="C330" s="0">
-        <v>5.9348871106894574</v>
+        <v>6.2772438772163008</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="0">
-        <v>0.10353659098497495</v>
+        <v>0.1001913053311793</v>
       </c>
       <c r="B331" s="0">
-        <v>0.040657711779351354</v>
+        <v>0.041921523346975763</v>
       </c>
       <c r="C331" s="0">
-        <v>5.8865066537798594</v>
+        <v>6.2581227901483052</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="0">
-        <v>0.10385033823038396</v>
+        <v>0.1004949153473344</v>
       </c>
       <c r="B332" s="0">
-        <v>0.040479452808609165</v>
+        <v>0.041849718022467467</v>
       </c>
       <c r="C332" s="0">
-        <v>5.8350024123678823</v>
+        <v>6.2367026864428965</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="0">
-        <v>0.10416408547579298</v>
+        <v>0.10079852536348949</v>
       </c>
       <c r="B333" s="0">
-        <v>0.040289100797408772</v>
+        <v>0.041769964669225904</v>
       </c>
       <c r="C333" s="0">
-        <v>5.7802539975682992</v>
+        <v>6.212954664797687</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="0">
-        <v>0.10447783272120199</v>
+        <v>0.10110213537964458</v>
       </c>
       <c r="B334" s="0">
-        <v>0.04008600171452241</v>
+        <v>0.041682106833519861</v>
       </c>
       <c r="C334" s="0">
-        <v>5.7221238700422807</v>
+        <v>6.1868458239498487</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="0">
-        <v>0.10479157996661101</v>
+        <v>0.10140574539579966</v>
       </c>
       <c r="B335" s="0">
-        <v>0.03986940458863128</v>
+        <v>0.041585967369190471</v>
       </c>
       <c r="C335" s="0">
-        <v>5.660454104458001</v>
+        <v>6.1583389111455604</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="0">
-        <v>0.10510532721202002</v>
+        <v>0.10170935541195476</v>
       </c>
       <c r="B336" s="0">
-        <v>0.039638441989603604</v>
+        <v>0.041481346461553513</v>
       </c>
       <c r="C336" s="0">
-        <v>5.5950622848057234</v>
+        <v>6.1273919065787572</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="0">
-        <v>0.10541907445742904</v>
+        <v>0.10201296542810985</v>
       </c>
       <c r="B337" s="0">
-        <v>0.039392104941197707</v>
+        <v>0.04136801929077185</v>
       </c>
       <c r="C337" s="0">
-        <v>5.5257362286707732</v>
+        <v>6.0939575320126469</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="0">
-        <v>0.10573282170283806</v>
+        <v>0.10231657544426494</v>
       </c>
       <c r="B338" s="0">
-        <v>0.039129210196973858</v>
+        <v>0.041245733264450142</v>
       </c>
       <c r="C338" s="0">
-        <v>5.4522271055293361</v>
+        <v>6.0579826688112961</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="0">
-        <v>0.10604656894824706</v>
+        <v>0.10262018546042002</v>
       </c>
       <c r="B339" s="0">
-        <v>0.03884835683290104</v>
+        <v>0.041114204730904817</v>
       </c>
       <c r="C339" s="0">
-        <v>5.3742403084011876</v>
+        <v>6.0194076667604106</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="0">
-        <v>0.10636031619365607</v>
+        <v>0.10292379547657511</v>
       </c>
       <c r="B340" s="0">
-        <v>0.038547867554828384</v>
+        <v>0.04097311506073216</v>
       </c>
       <c r="C340" s="0">
-        <v>5.2914231111186059</v>
+        <v>5.9781655200450592</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="0">
-        <v>0.1066740634390651</v>
+        <v>0.1032274054927302</v>
       </c>
       <c r="B341" s="0">
-        <v>0.038234300277794453</v>
+        <v>0.040822105952928421</v>
       </c>
       <c r="C341" s="0">
-        <v>5.2056871782084153</v>
+        <v>5.9341808801554583</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="0">
-        <v>0.10698781068447411</v>
+        <v>0.10353101550888527</v>
       </c>
       <c r="B342" s="0">
-        <v>0.037920553032385451</v>
+        <v>0.040660773780051146</v>
       </c>
       <c r="C342" s="0">
-        <v>5.1206029074333319</v>
+        <v>5.8873688667089672</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="0">
-        <v>0.10730155792988312</v>
+        <v>0.10383462552504037</v>
       </c>
       <c r="B343" s="0">
-        <v>0.037606805786976436</v>
+        <v>0.040488662730632313</v>
       </c>
       <c r="C343" s="0">
-        <v>5.0362197070279713</v>
+        <v>5.8376336253415167</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="0">
-        <v>0.10761530517529215</v>
+        <v>0.10413823554119547</v>
       </c>
       <c r="B344" s="0">
-        <v>0.037293058541567406</v>
+        <v>0.040305256430232209</v>
       </c>
       <c r="C344" s="0">
-        <v>4.9525375769923334</v>
+        <v>5.7848665656664782</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="0">
-        <v>0.10792905242070115</v>
+        <v>0.10444184555735055</v>
       </c>
       <c r="B345" s="0">
-        <v>0.036979311296158404</v>
+        <v>0.040109967616184884</v>
       </c>
       <c r="C345" s="0">
-        <v>4.869556517326429</v>
+        <v>5.7289441899367919</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="0">
-        <v>0.10824279966611017</v>
+        <v>0.10474545557350565</v>
       </c>
       <c r="B346" s="0">
-        <v>0.036665564050749389</v>
+        <v>0.039902125291641721</v>
       </c>
       <c r="C346" s="0">
-        <v>4.7872765280302483</v>
+        <v>5.6697253916188819</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="0">
-        <v>0.1085565469115192</v>
+        <v>0.10504906558966075</v>
       </c>
       <c r="B347" s="0">
-        <v>0.036351816805340359</v>
+        <v>0.039680958570975852</v>
       </c>
       <c r="C347" s="0">
-        <v>4.7056976091037894</v>
+        <v>5.6070480581800028</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="0">
-        <v>0.1088702941569282</v>
+        <v>0.10535267560581582</v>
       </c>
       <c r="B348" s="0">
-        <v>0.036038069559931357</v>
+        <v>0.039445576117839325</v>
       </c>
       <c r="C348" s="0">
-        <v>4.6248197605470649</v>
+        <v>5.5407247470374257</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="0">
-        <v>0.10918404140233723</v>
+        <v>0.10565628562197092</v>
       </c>
       <c r="B349" s="0">
-        <v>0.035724322314522328</v>
+        <v>0.039194939615646268</v>
       </c>
       <c r="C349" s="0">
-        <v>4.5446429823600614</v>
+        <v>5.4705371065632837</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="0">
-        <v>0.10949778864774622</v>
+        <v>0.10595989563812599</v>
       </c>
       <c r="B350" s="0">
-        <v>0.03541057506911334</v>
+        <v>0.038927829009202816</v>
       </c>
       <c r="C350" s="0">
-        <v>4.4651672745427922</v>
+        <v>5.3962285666119323</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="0">
-        <v>0.10981153589315525</v>
+        <v>0.10626350565428108</v>
       </c>
       <c r="B351" s="0">
-        <v>0.03509682782370431</v>
+        <v>0.038642796163950652</v>
       </c>
       <c r="C351" s="0">
-        <v>4.3863926370952413</v>
+        <v>5.3174945933422704</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="0">
-        <v>0.11012528313856428</v>
+        <v>0.10656711567043618</v>
       </c>
       <c r="B352" s="0">
-        <v>0.034783080578295281</v>
+        <v>0.038341248046423373</v>
       </c>
       <c r="C352" s="0">
-        <v>4.3083190700174159</v>
+        <v>5.2348285193150357</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="0">
-        <v>0.11043903038397328</v>
+        <v>0.10687072568659126</v>
       </c>
       <c r="B353" s="0">
-        <v>0.034469333332886279</v>
+        <v>0.0380376380302683</v>
       </c>
       <c r="C353" s="0">
-        <v>4.2309465733093239</v>
+        <v>5.1522514655168425</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="0">
-        <v>0.11075277762938229</v>
+        <v>0.10717433570274636</v>
       </c>
       <c r="B354" s="0">
-        <v>0.034155586087477263</v>
+        <v>0.0377340280141132</v>
       </c>
       <c r="C354" s="0">
-        <v>4.1542751469709547</v>
+        <v>5.0703309078244514</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="0">
-        <v>0.11106652487479129</v>
+        <v>0.10747794571890143</v>
       </c>
       <c r="B355" s="0">
-        <v>0.033841838842068262</v>
+        <v>0.037430417997958126</v>
       </c>
       <c r="C355" s="0">
-        <v>4.0783047910023162</v>
+        <v>4.9890668462378773</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="0">
-        <v>0.11138027212020032</v>
+        <v>0.10778155573505653</v>
       </c>
       <c r="B356" s="0">
-        <v>0.033528091596659232</v>
+        <v>0.037126807981803026</v>
       </c>
       <c r="C356" s="0">
-        <v>4.0030355054033961</v>
+        <v>4.9084592807571044</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="0">
-        <v>0.11169401936560934</v>
+        <v>0.10808516575121163</v>
       </c>
       <c r="B357" s="0">
-        <v>0.033214344351250216</v>
+        <v>0.036823197965647925</v>
       </c>
       <c r="C357" s="0">
-        <v>3.9284672901742077</v>
+        <v>4.8285082113821414</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="0">
-        <v>0.11200776661101834</v>
+        <v>0.1083887757673667</v>
       </c>
       <c r="B358" s="0">
-        <v>0.032900597105841215</v>
+        <v>0.036519587949492852</v>
       </c>
       <c r="C358" s="0">
-        <v>3.8546001453147483</v>
+        <v>4.7492136381129964</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="0">
-        <v>0.11232151385642737</v>
+        <v>0.10869238578352181</v>
       </c>
       <c r="B359" s="0">
-        <v>0.032586849860432185</v>
+        <v>0.036215977933337751</v>
       </c>
       <c r="C359" s="0">
-        <v>3.7814340708250085</v>
+        <v>4.6705755609496542</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="0">
-        <v>0.11263526110183637</v>
+        <v>0.10899599579967688</v>
       </c>
       <c r="B360" s="0">
-        <v>0.032273102615023183</v>
+        <v>0.035912367917182678</v>
       </c>
       <c r="C360" s="0">
-        <v>3.7089690667050022</v>
+        <v>4.5925939798921283</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="0">
-        <v>0.11294900834724539</v>
+        <v>0.10929960581583198</v>
       </c>
       <c r="B361" s="0">
-        <v>0.031959355369614168</v>
+        <v>0.035608757901027577</v>
       </c>
       <c r="C361" s="0">
-        <v>3.6372051329547186</v>
+        <v>4.5152688949404034</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="0">
-        <v>0.11326275559265442</v>
+        <v>0.10960321583198707</v>
       </c>
       <c r="B362" s="0">
-        <v>0.031645608124205138</v>
+        <v>0.03530514788487249</v>
       </c>
       <c r="C362" s="0">
-        <v>3.5661422695741592</v>
+        <v>4.4386003060944921</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="0">
-        <v>0.11357650283806342</v>
+        <v>0.10990682584814214</v>
       </c>
       <c r="B363" s="0">
-        <v>0.031331860878796136</v>
+        <v>0.035001537868717417</v>
       </c>
       <c r="C363" s="0">
-        <v>3.4957804765633322</v>
+        <v>4.3625882133543943</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="0">
-        <v>0.11389025008347245</v>
+        <v>0.11021043586429724</v>
       </c>
       <c r="B364" s="0">
-        <v>0.031018113633387107</v>
+        <v>0.034697927852562316</v>
       </c>
       <c r="C364" s="0">
-        <v>3.426119753922225</v>
+        <v>4.2872326167200985</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="0">
-        <v>0.11420399732888147</v>
+        <v>0.11051404588045234</v>
       </c>
       <c r="B365" s="0">
-        <v>0.030704366387978091</v>
+        <v>0.034394317836407215</v>
       </c>
       <c r="C365" s="0">
-        <v>3.3571601016508477</v>
+        <v>4.2125335161916144</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="0">
-        <v>0.11451774457429047</v>
+        <v>0.11081765589660741</v>
       </c>
       <c r="B366" s="0">
-        <v>0.030390619142569089</v>
+        <v>0.034090707820252142</v>
       </c>
       <c r="C366" s="0">
-        <v>3.2889015197492002</v>
+        <v>4.1384909117689448</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="0">
-        <v>0.1148314918196995</v>
+        <v>0.11112126591276252</v>
       </c>
       <c r="B367" s="0">
-        <v>0.03007687189716006</v>
+        <v>0.033787097804097041</v>
       </c>
       <c r="C367" s="0">
-        <v>3.2213440082172733</v>
+        <v>4.065104803452078</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="0">
-        <v>0.1151452390651085</v>
+        <v>0.11142487592891759</v>
       </c>
       <c r="B368" s="0">
-        <v>0.029763124651751058</v>
+        <v>0.033483487787941968</v>
       </c>
       <c r="C368" s="0">
-        <v>3.1544875670550789</v>
+        <v>3.9923751912410279</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="0">
-        <v>0.11545898631051751</v>
+        <v>0.11172848594507269</v>
       </c>
       <c r="B369" s="0">
-        <v>0.029449377406342042</v>
+        <v>0.033179877771786867</v>
       </c>
       <c r="C369" s="0">
-        <v>3.0883321962626078</v>
+        <v>3.9203020751357802</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="0">
-        <v>0.11577273355592654</v>
+        <v>0.11203209596122779</v>
       </c>
       <c r="B370" s="0">
-        <v>0.029135630160933013</v>
+        <v>0.032876267755631766</v>
       </c>
       <c r="C370" s="0">
-        <v>3.0228778958398608</v>
+        <v>3.848885455136343</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="0">
-        <v>0.11608648080133555</v>
+        <v>0.11233570597738286</v>
       </c>
       <c r="B371" s="0">
-        <v>0.028821882915524011</v>
+        <v>0.032572657739476693</v>
       </c>
       <c r="C371" s="0">
-        <v>2.9581246657868454</v>
+        <v>3.7781253312427214</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="0">
-        <v>0.11640022804674456</v>
+        <v>0.11263931599353795</v>
       </c>
       <c r="B372" s="0">
-        <v>0.028508135670114995</v>
+        <v>0.032269047723321606</v>
       </c>
       <c r="C372" s="0">
-        <v>2.8940725061035537</v>
+        <v>3.7080217034549059</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="0">
-        <v>0.11671397529215356</v>
+        <v>0.11294292600969304</v>
       </c>
       <c r="B373" s="0">
-        <v>0.028194388424705993</v>
+        <v>0.031965437707166519</v>
       </c>
       <c r="C373" s="0">
-        <v>2.8307214167899915</v>
+        <v>3.6385745717728999</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="0">
-        <v>0.11702772253756259</v>
+        <v>0.11324653602584812</v>
       </c>
       <c r="B374" s="0">
-        <v>0.027880641179296964</v>
+        <v>0.031661827691011432</v>
       </c>
       <c r="C374" s="0">
-        <v>2.7680713978461502</v>
+        <v>3.5697839361967043</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="0">
-        <v>0.11734146978297162</v>
+        <v>0.11355014604200323</v>
       </c>
       <c r="B375" s="0">
-        <v>0.027566893933887934</v>
+        <v>0.031358217674856331</v>
       </c>
       <c r="C375" s="0">
-        <v>2.7061224492720357</v>
+        <v>3.5016497967263143</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="0">
-        <v>0.11765521702838061</v>
+        <v>0.1138537560581583</v>
       </c>
       <c r="B376" s="0">
-        <v>0.027253146688478946</v>
+        <v>0.031054607658701258</v>
       </c>
       <c r="C376" s="0">
-        <v>2.6448745710676551</v>
+        <v>3.4341721533617404</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="0">
-        <v>0.11796896427378964</v>
+        <v>0.1141573660743134</v>
       </c>
       <c r="B377" s="0">
-        <v>0.026939399443069917</v>
+        <v>0.030750997642546157</v>
       </c>
       <c r="C377" s="0">
-        <v>2.5843277632329942</v>
+        <v>3.3673510061029703</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="0">
-        <v>0.11828271151919864</v>
+        <v>0.11446097609046847</v>
       </c>
       <c r="B378" s="0">
-        <v>0.026625652197660915</v>
+        <v>0.030447387626391084</v>
       </c>
       <c r="C378" s="0">
-        <v>2.5244820257680645</v>
+        <v>3.3011863549500151</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="0">
-        <v>0.11859645876460767</v>
+        <v>0.11476458610662357</v>
       </c>
       <c r="B379" s="0">
-        <v>0.026311904952251886</v>
+        <v>0.030143777610235983</v>
       </c>
       <c r="C379" s="0">
-        <v>2.4653373586728553</v>
+        <v>3.2356781999028636</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="0">
-        <v>0.11891020601001669</v>
+        <v>0.11506819612277867</v>
       </c>
       <c r="B380" s="0">
-        <v>0.02599815770684287</v>
+        <v>0.029840167594080883</v>
       </c>
       <c r="C380" s="0">
-        <v>2.4068937619473765</v>
+        <v>3.1708265409615222</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="0">
-        <v>0.11922395325542569</v>
+        <v>0.11537180613893375</v>
       </c>
       <c r="B381" s="0">
-        <v>0.025684410461433868</v>
+        <v>0.029536557577925809</v>
       </c>
       <c r="C381" s="0">
-        <v>2.3491512355916266</v>
+        <v>3.106631378125996</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="0">
-        <v>0.11953770050083472</v>
+        <v>0.11567541615508885</v>
       </c>
       <c r="B382" s="0">
-        <v>0.025370663216024839</v>
+        <v>0.029232947561770709</v>
       </c>
       <c r="C382" s="0">
-        <v>2.2921097796055974</v>
+        <v>3.0430927113962731</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="0">
-        <v>0.11985144774624373</v>
+        <v>0.11597902617124393</v>
       </c>
       <c r="B383" s="0">
-        <v>0.025056915970615823</v>
+        <v>0.028929337545615622</v>
       </c>
       <c r="C383" s="0">
-        <v>2.2357693939892975</v>
+        <v>2.9802105407723629</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="0">
-        <v>0.12016519499165274</v>
+        <v>0.11628263618739902</v>
       </c>
       <c r="B384" s="0">
-        <v>0.024743168725206821</v>
+        <v>0.028625727529460535</v>
       </c>
       <c r="C384" s="0">
-        <v>2.1801300787427267</v>
+        <v>2.9179848662542627</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" s="0">
-        <v>0.12047894223706176</v>
+        <v>0.11658624620355411</v>
       </c>
       <c r="B385" s="0">
-        <v>0.024429421479797792</v>
+        <v>0.028322117513305448</v>
       </c>
       <c r="C385" s="0">
-        <v>2.1251918338658777</v>
+        <v>2.8564156878419715</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="0">
-        <v>0.12079268948247077</v>
+        <v>0.11688985621970918</v>
       </c>
       <c r="B386" s="0">
-        <v>0.02411567423438879</v>
+        <v>0.028018507497150374</v>
       </c>
       <c r="C386" s="0">
-        <v>2.07095465935876</v>
+        <v>2.795503005535493</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" s="0">
-        <v>0.12110643672787978</v>
+        <v>0.11719346623586428</v>
       </c>
       <c r="B387" s="0">
-        <v>0.023801926988979774</v>
+        <v>0.027714897480995274</v>
       </c>
       <c r="C387" s="0">
-        <v>2.0174185552213659</v>
+        <v>2.7352468193348183</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="0">
-        <v>0.12142018397328881</v>
+        <v>0.11749707625201938</v>
       </c>
       <c r="B388" s="0">
-        <v>0.023488179743570745</v>
+        <v>0.027411287464840173</v>
       </c>
       <c r="C388" s="0">
-        <v>1.9645835214536962</v>
+        <v>2.6756471292399535</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="0">
-        <v>0.12173393121869781</v>
+        <v>0.11780068626817446</v>
       </c>
       <c r="B389" s="0">
-        <v>0.023174432498161743</v>
+        <v>0.0271076774486851</v>
       </c>
       <c r="C389" s="0">
-        <v>1.9124495580557579</v>
+        <v>2.6167039352509036</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="0">
-        <v>0.12204767846410683</v>
+        <v>0.11810429628432956</v>
       </c>
       <c r="B390" s="0">
-        <v>0.022860685252752727</v>
+        <v>0.026804067432529999</v>
       </c>
       <c r="C390" s="0">
-        <v>1.8610166650275441</v>
+        <v>2.5584172373676575</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="0">
-        <v>0.12236142570951583</v>
+        <v>0.11840790630048463</v>
       </c>
       <c r="B391" s="0">
-        <v>0.022546938007343725</v>
+        <v>0.026500457416374926</v>
       </c>
       <c r="C391" s="0">
-        <v>1.8102848423690587</v>
+        <v>2.5007870355902266</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" s="0">
-        <v>0.12267517295492486</v>
+        <v>0.11871151631663973</v>
       </c>
       <c r="B392" s="0">
-        <v>0.022233190761934696</v>
+        <v>0.026196847400219825</v>
       </c>
       <c r="C392" s="0">
-        <v>1.7602540900802952</v>
+        <v>2.4438133299186005</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="0">
-        <v>0.12298892020033389</v>
+        <v>0.11901512633279483</v>
       </c>
       <c r="B393" s="0">
-        <v>0.021919443516525666</v>
+        <v>0.025893237384064724</v>
       </c>
       <c r="C393" s="0">
-        <v>1.7109244081612587</v>
+        <v>2.3874961203527829</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="0">
-        <v>0.12330266744574289</v>
+        <v>0.11931873634894991</v>
       </c>
       <c r="B394" s="0">
-        <v>0.021605696271116665</v>
+        <v>0.025589627367909651</v>
       </c>
       <c r="C394" s="0">
-        <v>1.6622957966119527</v>
+        <v>2.3318354068927807</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="0">
-        <v>0.12361641469115191</v>
+        <v>0.11962234636510499</v>
       </c>
       <c r="B395" s="0">
-        <v>0.021291949025707649</v>
+        <v>0.025286017351754564</v>
       </c>
       <c r="C395" s="0">
-        <v>1.6143682554323711</v>
+        <v>2.2768311895385858</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="0">
-        <v>0.12393016193656091</v>
+        <v>0.11992595638126008</v>
       </c>
       <c r="B396" s="0">
-        <v>0.020978201780298647</v>
+        <v>0.024982407335599477</v>
       </c>
       <c r="C396" s="0">
-        <v>1.5671417846225182</v>
+        <v>2.2224834682901999</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="0">
-        <v>0.12424390918196994</v>
+        <v>0.12022956639741517</v>
       </c>
       <c r="B397" s="0">
-        <v>0.020667852944765606</v>
+        <v>0.02467879731944439</v>
       </c>
       <c r="C397" s="0">
-        <v>1.5211165766901274</v>
+        <v>2.1687922431476237</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="0">
-        <v>0.12455765642737895</v>
+        <v>0.12053317641357027</v>
       </c>
       <c r="B398" s="0">
-        <v>0.020374698030790842</v>
+        <v>0.024375187303289289</v>
       </c>
       <c r="C398" s="0">
-        <v>1.4782712658246284</v>
+        <v>2.1157575141108551</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" s="0">
-        <v>0.12487140367278796</v>
+        <v>0.12083678642972534</v>
       </c>
       <c r="B399" s="0">
-        <v>0.020098875964722117</v>
+        <v>0.024071577287134216</v>
       </c>
       <c r="C399" s="0">
-        <v>1.4385180435467821</v>
+        <v>2.0633792811799001</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="0">
-        <v>0.12518515091819699</v>
+        <v>0.12114039644588044</v>
       </c>
       <c r="B400" s="0">
-        <v>0.019839069475375139</v>
+        <v>0.023767967270979115</v>
       </c>
       <c r="C400" s="0">
-        <v>1.4015686353030339</v>
+        <v>2.0116575443547502</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="0">
-        <v>0.12549889816360602</v>
+        <v>0.12144400646203554</v>
       </c>
       <c r="B401" s="0">
-        <v>0.019594157308060113</v>
+        <v>0.023464357254824014</v>
       </c>
       <c r="C401" s="0">
-        <v>1.3671776632251187</v>
+        <v>1.9605923036354103</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="0">
-        <v>0.12581264540901502</v>
+        <v>0.12174761647819062</v>
       </c>
       <c r="B402" s="0">
-        <v>0.019363176473535436</v>
+        <v>0.023160747238668941</v>
       </c>
       <c r="C402" s="0">
-        <v>1.3351343846071946</v>
+        <v>1.9101835590218843</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="0">
-        <v>0.12612639265442402</v>
+        <v>0.12205122649434572</v>
       </c>
       <c r="B403" s="0">
-        <v>0.019145293466118589</v>
+        <v>0.02285713722251384</v>
       </c>
       <c r="C403" s="0">
-        <v>1.3052563932132639</v>
+        <v>1.8604313105141628</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="0">
-        <v>0.12644013989983302</v>
+        <v>0.12235483651050079</v>
       </c>
       <c r="B404" s="0">
-        <v>0.01893978197587564</v>
+        <v>0.022553527206358767</v>
       </c>
       <c r="C404" s="0">
-        <v>1.2773847417631892</v>
+        <v>1.8113355581122559</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="0">
-        <v>0.12675388714524205</v>
+        <v>0.12265844652665589</v>
       </c>
       <c r="B405" s="0">
-        <v>0.01874600538991418</v>
+        <v>0.022249917190203666</v>
       </c>
       <c r="C405" s="0">
-        <v>1.2513801124767472</v>
+        <v>1.7628963018161543</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="0">
-        <v>0.12706763439065108</v>
+        <v>0.12296205654281098</v>
       </c>
       <c r="B406" s="0">
-        <v>0.018563402883855898</v>
+        <v>0.021946307174048579</v>
       </c>
       <c r="C406" s="0">
-        <v>1.2271197733005748</v>
+        <v>1.715113541625864</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" s="0">
-        <v>0.12738138163606008</v>
+        <v>0.12326566655896605</v>
       </c>
       <c r="B407" s="0">
-        <v>0.018391478244757703</v>
+        <v>0.021642697157893506</v>
       </c>
       <c r="C407" s="0">
-        <v>1.2044951318913904</v>
+        <v>1.6679872775413858</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="0">
-        <v>0.12769512888146911</v>
+        <v>0.12356927657512115</v>
       </c>
       <c r="B408" s="0">
-        <v>0.018229790800158921</v>
+        <v>0.021339087141738405</v>
       </c>
       <c r="C408" s="0">
-        <v>1.1834097505085235</v>
+        <v>1.6215175095627123</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="0">
-        <v>0.12800887612687811</v>
+        <v>0.12387288659127622</v>
       </c>
       <c r="B409" s="0">
-        <v>0.018077947991048844</v>
+        <v>0.021035477125583332</v>
       </c>
       <c r="C409" s="0">
-        <v>1.1637777206656199</v>
+        <v>1.5757042376898531</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="0">
-        <v>0.12832262337228714</v>
+        <v>0.12417649660743132</v>
       </c>
       <c r="B410" s="0">
-        <v>0.017935599242460361</v>
+        <v>0.020733248439552834</v>
       </c>
       <c r="C410" s="0">
-        <v>1.1455223217577408</v>
+        <v>1.5307514244253249</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" s="0">
-        <v>0.12863637061769614</v>
+        <v>0.12448010662358643</v>
       </c>
       <c r="B411" s="0">
-        <v>0.017802430869026852</v>
+        <v>0.020445489477709113</v>
       </c>
       <c r="C411" s="0">
-        <v>1.1285749061820976</v>
+        <v>1.4885553685615216</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="0">
-        <v>0.12895011786310515</v>
+        <v>0.1247837166397415</v>
       </c>
       <c r="B412" s="0">
-        <v>0.017678161814026018</v>
+        <v>0.020174298429194368</v>
       </c>
       <c r="C412" s="0">
-        <v>1.1128739668609449</v>
+        <v>1.4493285604990447</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="0">
-        <v>0.12926386510851418</v>
+        <v>0.12508732665589659</v>
       </c>
       <c r="B413" s="0">
-        <v>0.017562540065781011</v>
+        <v>0.019918428211912052</v>
       </c>
       <c r="C413" s="0">
-        <v>1.0983643529988354</v>
+        <v>1.4127980871544275</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" s="0">
-        <v>0.12957761235392318</v>
+        <v>0.12539093667205167</v>
       </c>
       <c r="B414" s="0">
-        <v>0.017455339629297212</v>
+        <v>0.019676814562472882</v>
       </c>
       <c r="C414" s="0">
-        <v>1.0849966073488799</v>
+        <v>1.3787310437301437</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="0">
-        <v>0.12989135959933221</v>
+        <v>0.12569454668820676</v>
       </c>
       <c r="B415" s="0">
-        <v>0.01735635795680332</v>
+        <v>0.019448541259203332</v>
       </c>
       <c r="C415" s="0">
-        <v>1.0727264039066533</v>
+        <v>1.346926923072131</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="0">
-        <v>0.13020510684474124</v>
+        <v>0.12599815670436187</v>
       </c>
       <c r="B416" s="0">
-        <v>0.01726541376062872</v>
+        <v>0.019232813506064667</v>
       </c>
       <c r="C416" s="0">
-        <v>1.0615140692754119</v>
+        <v>1.3172117909716794</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="0">
-        <v>0.13051885409015024</v>
+        <v>0.12630176672051693</v>
       </c>
       <c r="B417" s="0">
-        <v>0.017182345147143264</v>
+        <v>0.019028937251407575</v>
       </c>
       <c r="C417" s="0">
-        <v>1.0513241742933312</v>
+        <v>1.2894337602545363</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="0">
-        <v>0.13083260133555924</v>
+        <v>0.12660537673667205</v>
       </c>
       <c r="B418" s="0">
-        <v>0.017107008022435082</v>
+        <v>0.01883630290044766</v>
       </c>
       <c r="C418" s="0">
-        <v>1.0421251851284938</v>
+        <v>1.2634594263976715</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="0">
-        <v>0.13114634858096827</v>
+        <v>0.12690898675282714</v>
       </c>
       <c r="B419" s="0">
-        <v>0.017039274729823497</v>
+        <v>0.018654372332930262</v>
       </c>
       <c r="C419" s="0">
-        <v>1.0338891651091899</v>
+        <v>1.2391710264579818</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="0">
-        <v>0.13146009582637727</v>
+        <v>0.12721259676898222</v>
       </c>
       <c r="B420" s="0">
-        <v>0.016979032886800867</v>
+        <v>0.018482668443195651</v>
       </c>
       <c r="C420" s="0">
-        <v>1.0265915201976794</v>
+        <v>1.2164641500064375</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="0">
-        <v>0.1317738430717863</v>
+        <v>0.12751620678513731</v>
       </c>
       <c r="B421" s="0">
-        <v>0.01692618439501728</v>
+        <v>0.018320766630556529</v>
       </c>
       <c r="C421" s="0">
-        <v>1.0202107823330482</v>
+        <v>1.1952458768711152</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="0">
-        <v>0.1320875903171953</v>
+        <v>0.1278198168012924</v>
       </c>
       <c r="B422" s="0">
-        <v>0.016880644601803371</v>
+        <v>0.018168287815730932</v>
       </c>
       <c r="C422" s="0">
-        <v>1.0147284259369953</v>
+        <v>1.1754332488442059</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="0">
-        <v>0.13240133756260433</v>
+        <v>0.12812342681744748</v>
       </c>
       <c r="B423" s="0">
-        <v>0.016842341595724328</v>
+        <v>0.018024892664503765</v>
       </c>
       <c r="C423" s="0">
-        <v>1.0101287137513049</v>
+        <v>1.1569520055805211</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="0">
-        <v>0.13271508480801336</v>
+        <v>0.12842703683360257</v>
       </c>
       <c r="B424" s="0">
-        <v>0.016811215621970292</v>
+        <v>0.017890276776106429</v>
       </c>
       <c r="C424" s="0">
-        <v>1.0063985689005854</v>
+        <v>1.1397355316161726</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="0">
-        <v>0.13302883205342236</v>
+        <v>0.12873064684975766</v>
       </c>
       <c r="B425" s="0">
-        <v>0.016787218606167095</v>
+        <v>0.017764166649806026</v>
       </c>
       <c r="C425" s="0">
-        <v>1.0035274706819493</v>
+        <v>1.1237239736916573</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="0">
-        <v>0.13334257929883137</v>
+        <v>0.12903425686591275</v>
       </c>
       <c r="B426" s="0">
-        <v>0.016770313777557208</v>
+        <v>0.01764631628481049</v>
       </c>
       <c r="C426" s="0">
-        <v>1.001507372101099</v>
+        <v>1.1088634966706319</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="0">
-        <v>0.13365632654424037</v>
+        <v>0.12933786688206783</v>
       </c>
       <c r="B427" s="0">
-        <v>0.01676047538455033</v>
+        <v>0.01753650429988237</v>
       </c>
       <c r="C427" s="0">
-        <v>1.0003326376227799</v>
+        <v>1.0951056531924122</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="0">
-        <v>0.1339700737896494</v>
+        <v>0.12964147689822292</v>
       </c>
       <c r="B428" s="0">
-        <v>0.016757688497454397</v>
+        <v>0.01743453148283141</v>
       </c>
       <c r="C428" s="0">
-        <v>1</v>
+        <v>1.0824068473997095</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="0">
-        <v>0.13428382103505843</v>
+        <v>0.12994508691437803</v>
       </c>
       <c r="B429" s="0">
-        <v>0.016761948894837134</v>
+        <v>0.017340218698311469</v>
       </c>
       <c r="C429" s="0">
-        <v>1.0005085354051386</v>
+        <v>1.0707278770781652</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="0">
-        <v>0.13459756828046743</v>
+        <v>0.13024869693053309</v>
       </c>
       <c r="B430" s="0">
-        <v>0.01677326303149132</v>
+        <v>0.017253405096498003</v>
       </c>
       <c r="C430" s="0">
-        <v>1.0018596564193929</v>
+        <v>1.0600335416409723</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="0">
-        <v>0.13491131552587646</v>
+        <v>0.13055230694668821</v>
       </c>
       <c r="B431" s="0">
-        <v>0.016791648087434871</v>
+        <v>0.017173946576291399</v>
       </c>
       <c r="C431" s="0">
-        <v>1.004057122756066</v>
+        <v>1.0502923058142848</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" s="0">
-        <v>0.13522506277128546</v>
+        <v>0.13085591696284327</v>
       </c>
       <c r="B432" s="0">
-        <v>0.016817132098816395</v>
+        <v>0.017101714465427298</v>
       </c>
       <c r="C432" s="0">
-        <v>1.0071070699082274</v>
+        <v>1.0414760107908168</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="0">
-        <v>0.13553881001669446</v>
+        <v>0.13115952697899838</v>
       </c>
       <c r="B433" s="0">
-        <v>0.016849754173064394</v>
+        <v>0.017036594386827107</v>
       </c>
       <c r="C433" s="0">
-        <v>1.0110180562324471</v>
+        <v>1.0335596261405102</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="0">
-        <v>0.13585255726210349</v>
+        <v>0.13146313699515347</v>
       </c>
       <c r="B434" s="0">
-        <v>0.016889564792161443</v>
+        <v>0.016978485286104277</v>
       </c>
       <c r="C434" s="0">
-        <v>1.0158011293179845</v>
+        <v>1.0265210369887239</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="0">
-        <v>0.13616630450751249</v>
+        <v>0.13176674701130853</v>
       </c>
       <c r="B435" s="0">
-        <v>0.016936626209594866</v>
+        <v>0.016927298599660294</v>
       </c>
       <c r="C435" s="0">
-        <v>1.021469912856362</v>
+        <v>1.0203408619612715</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="0">
-        <v>0.13648005175292152</v>
+        <v>0.13207035702746364</v>
       </c>
       <c r="B436" s="0">
-        <v>0.016991012948391005</v>
+        <v>0.016882957546497768</v>
       </c>
       <c r="C436" s="0">
-        <v>1.0280407156322902</v>
+        <v>1.0150022982038691</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="0">
-        <v>0.13679379899833055</v>
+        <v>0.13237396704361873</v>
       </c>
       <c r="B437" s="0">
-        <v>0.017052812409748694</v>
+        <v>0.016845396529923687</v>
       </c>
       <c r="C437" s="0">
-        <v>1.0355326647183662</v>
+        <v>1.0104909904500872</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="0">
-        <v>0.13710754624373955</v>
+        <v>0.13267757705977382</v>
       </c>
       <c r="B438" s="0">
-        <v>0.017122125604231205</v>
+        <v>0.016814560637855781</v>
       </c>
       <c r="C438" s="0">
-        <v>1.0439678654907501</v>
+        <v>1.0067949216677401</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" s="0">
-        <v>0.13742129348914858</v>
+        <v>0.1329811870759289</v>
       </c>
       <c r="B439" s="0">
-        <v>0.017197128055841251</v>
+        <v>0.016790405232587895</v>
       </c>
       <c r="C439" s="0">
-        <v>1.0531339755519005</v>
+        <v>1.003904323282603</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="0">
-        <v>0.13773504073455758</v>
+        <v>0.13328479709208399</v>
       </c>
       <c r="B440" s="0">
-        <v>0.017272452105183852</v>
+        <v>0.016772895622703281</v>
       </c>
       <c r="C440" s="0">
-        <v>1.062379710230527</v>
+        <v>1.0018116033794815</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="0">
-        <v>0.13804878797996659</v>
+        <v>0.13358840710823908</v>
       </c>
       <c r="B441" s="0">
-        <v>0.017347776154526446</v>
+        <v>0.016762006811417936</v>
       </c>
       <c r="C441" s="0">
-        <v>1.0716658530703131</v>
+        <v>1.0005112916293451</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="0">
-        <v>0.13836253522537562</v>
+        <v>0.13389201712439419</v>
       </c>
       <c r="B442" s="0">
-        <v>0.017423100203869054</v>
+        <v>0.016757723317047228</v>
       </c>
       <c r="C442" s="0">
-        <v>1.0809924040712617</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="0">
-        <v>0.13867628247078462</v>
+        <v>0.13419562714054925</v>
       </c>
       <c r="B443" s="0">
-        <v>0.017498424253211648</v>
+        <v>0.01676003906256536</v>
       </c>
       <c r="C443" s="0">
-        <v>1.0903593632333688</v>
+        <v>1.0002763985871419</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="0">
-        <v>0.13899002971619365</v>
+        <v>0.13449923715670434</v>
       </c>
       <c r="B444" s="0">
-        <v>0.017573748302554256</v>
+        <v>0.016768957332411384</v>
       </c>
       <c r="C444" s="0">
-        <v>1.0997667305566383</v>
+        <v>1.0013412061617251</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="0">
-        <v>0.13930377696160265</v>
+        <v>0.13480284717285942</v>
       </c>
       <c r="B445" s="0">
-        <v>0.017649072351896857</v>
+        <v>0.016784490795823164</v>
       </c>
       <c r="C445" s="0">
-        <v>1.1092145060410676</v>
+        <v>1.0031971952763983</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="0">
-        <v>0.13961752420701168</v>
+        <v>0.13510645718901451</v>
       </c>
       <c r="B446" s="0">
-        <v>0.017724396401239458</v>
+        <v>0.016806661597087262</v>
       </c>
       <c r="C446" s="0">
-        <v>1.1187026896866574</v>
+        <v>1.0058492120159102</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="0">
-        <v>0.13993127145242071</v>
+        <v>0.13541006720516963</v>
       </c>
       <c r="B447" s="0">
-        <v>0.017799720450582059</v>
+        <v>0.016835501514210583</v>
       </c>
       <c r="C447" s="0">
-        <v>1.1282312814934077</v>
+        <v>1.0093042107210164</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="0">
-        <v>0.14024501869782968</v>
+        <v>0.13571367722132469</v>
       </c>
       <c r="B448" s="0">
-        <v>0.017875044499924653</v>
+        <v>0.016871052188683105</v>
       </c>
       <c r="C448" s="0">
-        <v>1.1378002814613175</v>
+        <v>1.0135713042700611</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="0">
-        <v>0.14055876594323871</v>
+        <v>0.1360172872374798</v>
       </c>
       <c r="B449" s="0">
-        <v>0.017950368549267261</v>
+        <v>0.016913365430245995</v>
       </c>
       <c r="C449" s="0">
-        <v>1.1474096895903898</v>
+        <v>1.0186618307748285</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="0">
-        <v>0.14087251318864771</v>
+        <v>0.13632089725363486</v>
       </c>
       <c r="B450" s="0">
-        <v>0.018025692598609856</v>
+        <v>0.016962503601945386</v>
       </c>
       <c r="C450" s="0">
-        <v>1.1570595058806208</v>
+        <v>1.024589437846221</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="0">
-        <v>0.14118626043405674</v>
+        <v>0.13662450726978997</v>
       </c>
       <c r="B451" s="0">
-        <v>0.018101016647952464</v>
+        <v>0.017018540092285768</v>
       </c>
       <c r="C451" s="0">
-        <v>1.1667497303320142</v>
+        <v>1.0313701859209195</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="0">
-        <v>0.14150000767946577</v>
+        <v>0.13692811728594506</v>
       </c>
       <c r="B452" s="0">
-        <v>0.018176340697295065</v>
+        <v>0.017081559883051413</v>
       </c>
       <c r="C452" s="0">
-        <v>1.1764803629445673</v>
+        <v>1.0390226725241805</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="0">
-        <v>0.14181375492487477</v>
+        <v>0.13723172730210015</v>
       </c>
       <c r="B453" s="0">
-        <v>0.018251664746637666</v>
+        <v>0.017151617240891117</v>
       </c>
       <c r="C453" s="0">
-        <v>1.1862514037182808</v>
+        <v>1.0475629293301372</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="0">
-        <v>0.1421275021702838</v>
+        <v>0.13753533731825524</v>
       </c>
       <c r="B454" s="0">
-        <v>0.018326988795980267</v>
+        <v>0.017224507556813925</v>
       </c>
       <c r="C454" s="0">
-        <v>1.1960628526531543</v>
+        <v>1.0564856381099088</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="0">
-        <v>0.14244124941569281</v>
+        <v>0.13783894733441032</v>
       </c>
       <c r="B455" s="0">
-        <v>0.018402312845322868</v>
+        <v>0.017297397872736733</v>
       </c>
       <c r="C455" s="0">
-        <v>1.2059147097491889</v>
+        <v>1.0654461858878614</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="0">
-        <v>0.14275499666110181</v>
+        <v>0.13814255735056541</v>
       </c>
       <c r="B456" s="0">
-        <v>0.018477636894665462</v>
+        <v>0.01737028818865954</v>
       </c>
       <c r="C456" s="0">
-        <v>1.2158069750063831</v>
+        <v>1.0744445726639949</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="0">
-        <v>0.14306874390651084</v>
+        <v>0.1384461673667205</v>
       </c>
       <c r="B457" s="0">
-        <v>0.01855296094400807</v>
+        <v>0.017443178504582348</v>
       </c>
       <c r="C457" s="0">
-        <v>1.2257396484247398</v>
+        <v>1.0834807984383095</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="0">
-        <v>0.14338249115191984</v>
+        <v>0.13874977738287558</v>
       </c>
       <c r="B458" s="0">
-        <v>0.018628284993350664</v>
+        <v>0.017516068820505156</v>
       </c>
       <c r="C458" s="0">
-        <v>1.235712730004255</v>
+        <v>1.0925548632108051</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="0">
-        <v>0.14369623839732887</v>
+        <v>0.13905338739903067</v>
       </c>
       <c r="B459" s="0">
-        <v>0.018703609042693272</v>
+        <v>0.017588959136427957</v>
       </c>
       <c r="C459" s="0">
-        <v>1.2457262197449328</v>
+        <v>1.1016667669814806</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="0">
-        <v>0.1440099856427379</v>
+        <v>0.13935699741518579</v>
       </c>
       <c r="B460" s="0">
-        <v>0.018778933092035873</v>
+        <v>0.017661849452350772</v>
       </c>
       <c r="C460" s="0">
-        <v>1.25578011764677</v>
+        <v>1.1108165097503389</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="0">
-        <v>0.1443237328881469</v>
+        <v>0.13966060743134085</v>
       </c>
       <c r="B461" s="0">
-        <v>0.018854257141378474</v>
+        <v>0.017734739768273573</v>
       </c>
       <c r="C461" s="0">
-        <v>1.2658744237097679</v>
+        <v>1.1200040915173763</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="0">
-        <v>0.1446374801335559</v>
+        <v>0.13996421744749596</v>
       </c>
       <c r="B462" s="0">
-        <v>0.018929581190721068</v>
+        <v>0.017807630084196387</v>
       </c>
       <c r="C462" s="0">
-        <v>1.2760091379339253</v>
+        <v>1.1292295122825968</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="0">
-        <v>0.1449512273789649</v>
+        <v>0.14026782746365102</v>
       </c>
       <c r="B463" s="0">
-        <v>0.019004905240063669</v>
+        <v>0.017880520400119188</v>
       </c>
       <c r="C463" s="0">
-        <v>1.2861842603192444</v>
+        <v>1.1384927720459963</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" s="0">
-        <v>0.14526497462437393</v>
+        <v>0.14057143747980613</v>
       </c>
       <c r="B464" s="0">
-        <v>0.019080229289406271</v>
+        <v>0.017953410716042003</v>
       </c>
       <c r="C464" s="0">
-        <v>1.2963997908657239</v>
+        <v>1.1477938708075786</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="0">
-        <v>0.14557872186978296</v>
+        <v>0.14087504749596122</v>
       </c>
       <c r="B465" s="0">
-        <v>0.019155553338748879</v>
+        <v>0.018026301031964811</v>
       </c>
       <c r="C465" s="0">
-        <v>1.306655729573365</v>
+        <v>1.1571328085673409</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" s="0">
-        <v>0.14589246911519196</v>
+        <v>0.14117865751211631</v>
       </c>
       <c r="B466" s="0">
-        <v>0.019230877388091473</v>
+        <v>0.018099191347887619</v>
       </c>
       <c r="C466" s="0">
-        <v>1.3169520764421645</v>
+        <v>1.1665095853252843</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="0">
-        <v>0.14620621636060099</v>
+        <v>0.14148226752827139</v>
       </c>
       <c r="B467" s="0">
-        <v>0.019306201437434081</v>
+        <v>0.018172081663810426</v>
       </c>
       <c r="C467" s="0">
-        <v>1.3272888314721265</v>
+        <v>1.1759242010814086</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="0">
-        <v>0.14651996360601</v>
+        <v>0.14178587754442648</v>
       </c>
       <c r="B468" s="0">
-        <v>0.019381525486776675</v>
+        <v>0.018244971979733234</v>
       </c>
       <c r="C468" s="0">
-        <v>1.3376659946632472</v>
+        <v>1.1853766558357139</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="0">
-        <v>0.14683371085141903</v>
+        <v>0.14208948756058157</v>
       </c>
       <c r="B469" s="0">
-        <v>0.019456849536119283</v>
+        <v>0.018317862295656042</v>
       </c>
       <c r="C469" s="0">
-        <v>1.3480835660155299</v>
+        <v>1.1948669495882003</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="0">
-        <v>0.14714745809682803</v>
+        <v>0.14239309757673666</v>
       </c>
       <c r="B470" s="0">
-        <v>0.019532173585461877</v>
+        <v>0.01839075261157885</v>
       </c>
       <c r="C470" s="0">
-        <v>1.3585415455289716</v>
+        <v>1.2043950823388676</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="0">
-        <v>0.14746120534223703</v>
+        <v>0.14269670759289174</v>
       </c>
       <c r="B471" s="0">
-        <v>0.019607497634804478</v>
+        <v>0.018463642927501651</v>
       </c>
       <c r="C471" s="0">
-        <v>1.369039933203575</v>
+        <v>1.2139610540877148</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" s="0">
-        <v>0.14777495258764606</v>
+        <v>0.14300031760904683</v>
       </c>
       <c r="B472" s="0">
-        <v>0.019682821684147079</v>
+        <v>0.018536533243424459</v>
       </c>
       <c r="C472" s="0">
-        <v>1.3795787290393387</v>
+        <v>1.2235648648347441</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="0">
-        <v>0.14808869983305509</v>
+        <v>0.14330392762520194</v>
       </c>
       <c r="B473" s="0">
-        <v>0.019758145733489687</v>
+        <v>0.018609423559347273</v>
       </c>
       <c r="C473" s="0">
-        <v>1.3901579330362641</v>
+        <v>1.2332065145799553</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="0">
-        <v>0.14840244707846409</v>
+        <v>0.143607537641357</v>
       </c>
       <c r="B474" s="0">
-        <v>0.019833469782832281</v>
+        <v>0.018682313875270074</v>
       </c>
       <c r="C474" s="0">
-        <v>1.4007775451943481</v>
+        <v>1.2428860033233455</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="0">
-        <v>0.14871619432387312</v>
+        <v>0.14391114765751212</v>
       </c>
       <c r="B475" s="0">
-        <v>0.019908793832174889</v>
+        <v>0.018755204191192889</v>
       </c>
       <c r="C475" s="0">
-        <v>1.4114375655135944</v>
+        <v>1.2526033310649185</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="0">
-        <v>0.14902994156928212</v>
+        <v>0.14421475767366718</v>
       </c>
       <c r="B476" s="0">
-        <v>0.019984117881517483</v>
+        <v>0.01882809450711569</v>
       </c>
       <c r="C476" s="0">
-        <v>1.4221379939939995</v>
+        <v>1.2623584978046707</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="0">
-        <v>0.14934368881469112</v>
+        <v>0.14451836768982229</v>
       </c>
       <c r="B477" s="0">
-        <v>0.020059441930860084</v>
+        <v>0.018900984823038505</v>
       </c>
       <c r="C477" s="0">
-        <v>1.432878830635566</v>
+        <v>1.2721515035426059</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="0">
-        <v>0.14965743606010015</v>
+        <v>0.14482197770597738</v>
       </c>
       <c r="B478" s="0">
-        <v>0.020134765980202685</v>
+        <v>0.018973875138961312</v>
       </c>
       <c r="C478" s="0">
-        <v>1.4436600754382931</v>
+        <v>1.2819823482787209</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="0">
-        <v>0.14997118330550915</v>
+        <v>0.14512558772213244</v>
       </c>
       <c r="B479" s="0">
-        <v>0.020210090029545286</v>
+        <v>0.019046765454884113</v>
       </c>
       <c r="C479" s="0">
-        <v>1.4544817284021807</v>
+        <v>1.2918510320130161</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="0">
-        <v>0.15028493055091818</v>
+        <v>0.14542919773828755</v>
       </c>
       <c r="B480" s="0">
-        <v>0.020285414078887888</v>
+        <v>0.019119655770806928</v>
       </c>
       <c r="C480" s="0">
-        <v>1.4653437895272288</v>
+        <v>1.3017575547454943</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="0">
-        <v>0.15059867779632719</v>
+        <v>0.14573280775444261</v>
       </c>
       <c r="B481" s="0">
-        <v>0.020360738128230489</v>
+        <v>0.019192546086729729</v>
       </c>
       <c r="C481" s="0">
-        <v>1.4762462588134375</v>
+        <v>1.3117019164761512</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="0">
-        <v>0.15091242504173622</v>
+        <v>0.14603641777059773</v>
       </c>
       <c r="B482" s="0">
-        <v>0.02043606217757309</v>
+        <v>0.019265436402652544</v>
       </c>
       <c r="C482" s="0">
-        <v>1.4871891362608067</v>
+        <v>1.3216841172049914</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="0">
-        <v>0.15122617228714525</v>
+        <v>0.14634002778675281</v>
       </c>
       <c r="B483" s="0">
-        <v>0.020511386226915698</v>
+        <v>0.019338326718575344</v>
       </c>
       <c r="C483" s="0">
-        <v>1.4981724218693371</v>
+        <v>1.3317041569320103</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="0">
-        <v>0.15153991953255425</v>
+        <v>0.1466436378029079</v>
       </c>
       <c r="B484" s="0">
-        <v>0.020586710276258292</v>
+        <v>0.019411217034498152</v>
       </c>
       <c r="C484" s="0">
-        <v>1.509196115639027</v>
+        <v>1.3417620356572113</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="0">
-        <v>0.15185366677796325</v>
+        <v>0.14694724781906299</v>
       </c>
       <c r="B485" s="0">
-        <v>0.020662034325600893</v>
+        <v>0.01948410735042096</v>
       </c>
       <c r="C485" s="0">
-        <v>1.5202602175698772</v>
+        <v>1.3518577533805933</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="0">
-        <v>0.15216741402337225</v>
+        <v>0.14725085783521808</v>
       </c>
       <c r="B486" s="0">
-        <v>0.020737358374943487</v>
+        <v>0.019556997666343768</v>
       </c>
       <c r="C486" s="0">
-        <v>1.531364727661888</v>
+        <v>1.3619913101021561</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="0">
-        <v>0.15248116126878128</v>
+        <v>0.14755446785137316</v>
       </c>
       <c r="B487" s="0">
-        <v>0.020812682424286095</v>
+        <v>0.019629887982266576</v>
       </c>
       <c r="C487" s="0">
-        <v>1.5425096459150607</v>
+        <v>1.3721627058219002</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="0">
-        <v>0.15279490851419031</v>
+        <v>0.14785807786752825</v>
       </c>
       <c r="B488" s="0">
-        <v>0.020888006473628696</v>
+        <v>0.019702778298189384</v>
       </c>
       <c r="C488" s="0">
-        <v>1.5536949723293931</v>
+        <v>1.3823719405398252</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="0">
-        <v>0.15310865575959931</v>
+        <v>0.14816168788368334</v>
       </c>
       <c r="B489" s="0">
-        <v>0.020963330522971297</v>
+        <v>0.019775668614112191</v>
       </c>
       <c r="C489" s="0">
-        <v>1.5649207069048861</v>
+        <v>1.3926190142559309</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="0">
-        <v>0.15342240300500834</v>
+        <v>0.14846529789983842</v>
       </c>
       <c r="B490" s="0">
-        <v>0.021038654572313898</v>
+        <v>0.019848558930034999</v>
       </c>
       <c r="C490" s="0">
-        <v>1.5761868496415397</v>
+        <v>1.4029039269702179</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="0">
-        <v>0.15373615025041737</v>
+        <v>0.14876890791599354</v>
       </c>
       <c r="B491" s="0">
-        <v>0.021113978621656506</v>
+        <v>0.019921449245957814</v>
       </c>
       <c r="C491" s="0">
-        <v>1.5874934005393548</v>
+        <v>1.4132266786826868</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="0">
-        <v>0.15404989749582634</v>
+        <v>0.1490725179321486</v>
       </c>
       <c r="B492" s="0">
-        <v>0.021189302670999093</v>
+        <v>0.019994339561880615</v>
       </c>
       <c r="C492" s="0">
-        <v>1.5988403595983274</v>
+        <v>1.4235872693933345</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="0">
-        <v>0.15436364474123537</v>
+        <v>0.14937612794830371</v>
       </c>
       <c r="B493" s="0">
-        <v>0.021264626720341701</v>
+        <v>0.02006722987780343</v>
       </c>
       <c r="C493" s="0">
-        <v>1.6102277268184637</v>
+        <v>1.4339856991021653</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="0">
-        <v>0.15467739198664438</v>
+        <v>0.14967973796445877</v>
       </c>
       <c r="B494" s="0">
-        <v>0.021339950769684295</v>
+        <v>0.02014012019372623</v>
       </c>
       <c r="C494" s="0">
-        <v>1.6216555021997583</v>
+        <v>1.4444219678091752</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="0">
-        <v>0.15499113923205341</v>
+        <v>0.14998334798061389</v>
       </c>
       <c r="B495" s="0">
-        <v>0.021415274819026903</v>
+        <v>0.020213010509649038</v>
       </c>
       <c r="C495" s="0">
-        <v>1.6331236857422158</v>
+        <v>1.454896075514367</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="0">
-        <v>0.15530488647746243</v>
+        <v>0.15028695799676897</v>
       </c>
       <c r="B496" s="0">
-        <v>0.021490598868369504</v>
+        <v>0.020285900825571846</v>
       </c>
       <c r="C496" s="0">
-        <v>1.6446322774458326</v>
+        <v>1.4654080222177397</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="0">
-        <v>0.15561863372287144</v>
+        <v>0.15059056801292406</v>
       </c>
       <c r="B497" s="0">
-        <v>0.021565922917712106</v>
+        <v>0.020358791141494654</v>
       </c>
       <c r="C497" s="0">
-        <v>1.6561812773106099</v>
+        <v>1.4759578079192934</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="0">
-        <v>0.15593238096828047</v>
+        <v>0.15089417802907915</v>
       </c>
       <c r="B498" s="0">
-        <v>0.021641246967054707</v>
+        <v>0.020431681457417462</v>
       </c>
       <c r="C498" s="0">
-        <v>1.6677706853365479</v>
+        <v>1.4865454326190282</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="0">
-        <v>0.15624612821368947</v>
+        <v>0.15119778804523423</v>
       </c>
       <c r="B499" s="0">
-        <v>0.021716571016397308</v>
+        <v>0.02050457177334027</v>
       </c>
       <c r="C499" s="0">
-        <v>1.6794005015236457</v>
+        <v>1.4971708963169439</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="0">
-        <v>0.15655987545909847</v>
+        <v>0.15150139806138932</v>
       </c>
       <c r="B500" s="0">
-        <v>0.021791895065739902</v>
+        <v>0.020577462089263077</v>
       </c>
       <c r="C500" s="0">
-        <v>1.6910707258719042</v>
+        <v>1.5078341990130406</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="0">
-        <v>0.1568736227045075</v>
+        <v>0.15180500807754441</v>
       </c>
       <c r="B501" s="0">
-        <v>0.02186721911508251</v>
+        <v>0.020650352405185885</v>
       </c>
       <c r="C501" s="0">
-        <v>1.7027813583813243</v>
+        <v>1.5185353407073183</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="0">
-        <v>0.1571873699499165</v>
+        <v>0.15210861809369949</v>
       </c>
       <c r="B502" s="0">
-        <v>0.021942543164425104</v>
+        <v>0.020723242721108693</v>
       </c>
       <c r="C502" s="0">
-        <v>1.7145323990519033</v>
+        <v>1.5292743213997768</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" s="0">
-        <v>0.15750111719532553</v>
+        <v>0.15241222810985458</v>
       </c>
       <c r="B503" s="0">
-        <v>0.022017867213767712</v>
+        <v>0.020796133037031501</v>
       </c>
       <c r="C503" s="0">
-        <v>1.7263238478836449</v>
+        <v>1.5400511410904165</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="0">
-        <v>0.15781486444073453</v>
+        <v>0.15271583812600967</v>
       </c>
       <c r="B504" s="0">
-        <v>0.022093191263110306</v>
+        <v>0.020869023352954309</v>
       </c>
       <c r="C504" s="0">
-        <v>1.738155704876545</v>
+        <v>1.5508657997792372</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="0">
-        <v>0.15812861168614356</v>
+        <v>0.15301944814216476</v>
       </c>
       <c r="B505" s="0">
-        <v>0.022168515312452914</v>
+        <v>0.020941913668877116</v>
       </c>
       <c r="C505" s="0">
-        <v>1.7500279700306078</v>
+        <v>1.5617182974662387</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" s="0">
-        <v>0.15844235893155259</v>
+        <v>0.15332305815831987</v>
       </c>
       <c r="B506" s="0">
-        <v>0.022243839361795515</v>
+        <v>0.021014803984799931</v>
       </c>
       <c r="C506" s="0">
-        <v>1.76194064334583</v>
+        <v>1.5726086341514225</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="0">
-        <v>0.15875610617696157</v>
+        <v>0.15362666817447493</v>
       </c>
       <c r="B507" s="0">
-        <v>0.022319163411138109</v>
+        <v>0.021087694300722732</v>
       </c>
       <c r="C507" s="0">
-        <v>1.7738937248222118</v>
+        <v>1.5835368098347849</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="0">
-        <v>0.15906985342237059</v>
+        <v>0.15393027819063004</v>
       </c>
       <c r="B508" s="0">
-        <v>0.022394487460480717</v>
+        <v>0.02116058461664554</v>
       </c>
       <c r="C508" s="0">
-        <v>1.7858872144597562</v>
+        <v>1.5945028245163293</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="0">
-        <v>0.15938360066777962</v>
+        <v>0.15423388820678513</v>
       </c>
       <c r="B509" s="0">
-        <v>0.022469811509823318</v>
+        <v>0.021233474932568348</v>
       </c>
       <c r="C509" s="0">
-        <v>1.79792111225846</v>
+        <v>1.605506678196055</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="0">
-        <v>0.15969734791318863</v>
+        <v>0.15453749822294022</v>
       </c>
       <c r="B510" s="0">
-        <v>0.022545135559165919</v>
+        <v>0.021306365248491155</v>
       </c>
       <c r="C510" s="0">
-        <v>1.8099954182183244</v>
+        <v>1.6165483708739614</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="0">
-        <v>0.16001109515859766</v>
+        <v>0.1548411082390953</v>
       </c>
       <c r="B511" s="0">
-        <v>0.02262045960850852</v>
+        <v>0.021379255564413963</v>
       </c>
       <c r="C511" s="0">
-        <v>1.8221101323393494</v>
+        <v>1.6276279025500489</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="0">
-        <v>0.16032484240400666</v>
+        <v>0.15514471825525039</v>
       </c>
       <c r="B512" s="0">
-        <v>0.022695783657851121</v>
+        <v>0.021452145880336771</v>
       </c>
       <c r="C512" s="0">
-        <v>1.834265254621535</v>
+        <v>1.6387452732243173</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="0">
-        <v>0.16063858964941569</v>
+        <v>0.15544832827140548</v>
       </c>
       <c r="B513" s="0">
-        <v>0.022771107707193722</v>
+        <v>0.021525036196259579</v>
       </c>
       <c r="C513" s="0">
-        <v>1.8464607850648809</v>
+        <v>1.6499004828967667</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" s="0">
-        <v>0.16095233689482469</v>
+        <v>0.15575193828756057</v>
       </c>
       <c r="B514" s="0">
-        <v>0.022846431756536324</v>
+        <v>0.021597926512182387</v>
       </c>
       <c r="C514" s="0">
-        <v>1.858696723669387</v>
+        <v>1.6610935315673971</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="0">
-        <v>0.16126608414023369</v>
+        <v>0.15605554830371565</v>
       </c>
       <c r="B515" s="0">
-        <v>0.022921755805878918</v>
+        <v>0.021670816828105195</v>
       </c>
       <c r="C515" s="0">
-        <v>1.8709730704350536</v>
+        <v>1.6723244192362086</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="0">
-        <v>0.16157983138564272</v>
+        <v>0.15635915831987074</v>
       </c>
       <c r="B516" s="0">
-        <v>0.022997079855221526</v>
+        <v>0.021743707144028002</v>
       </c>
       <c r="C516" s="0">
-        <v>1.8832898253618817</v>
+        <v>1.683593145903201</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="0">
-        <v>0.16189357863105172</v>
+        <v>0.15666276833602583</v>
       </c>
       <c r="B517" s="0">
-        <v>0.02307240390456412</v>
+        <v>0.02181659745995081</v>
       </c>
       <c r="C517" s="0">
-        <v>1.8956469884498688</v>
+        <v>1.6948997115683744</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" s="0">
-        <v>0.16220732587646075</v>
+        <v>0.15696637835218091</v>
       </c>
       <c r="B518" s="0">
-        <v>0.023147727953906728</v>
+        <v>0.021889487775873618</v>
       </c>
       <c r="C518" s="0">
-        <v>1.9080445596990188</v>
+        <v>1.7062441162317286</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" s="0">
-        <v>0.16252107312186978</v>
+        <v>0.15726998836833603</v>
       </c>
       <c r="B519" s="0">
-        <v>0.023223052003249329</v>
+        <v>0.021962378091796426</v>
       </c>
       <c r="C519" s="0">
-        <v>1.9204825391093281</v>
+        <v>1.717626359893264</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="0">
-        <v>0.16283482036727878</v>
+        <v>0.15757359838449109</v>
       </c>
       <c r="B520" s="0">
-        <v>0.02329837605259193</v>
+        <v>0.022035268407719227</v>
       </c>
       <c r="C520" s="0">
-        <v>1.9329609266807979</v>
+        <v>1.729046442552979</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="0">
-        <v>0.16314856761268781</v>
+        <v>0.1578772084006462</v>
       </c>
       <c r="B521" s="0">
-        <v>0.023373700101934531</v>
+        <v>0.022108158723642042</v>
       </c>
       <c r="C521" s="0">
-        <v>1.9454797224134282</v>
+        <v>1.7405043642108775</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="0">
-        <v>0.16346231485809681</v>
+        <v>0.15818081841680129</v>
       </c>
       <c r="B522" s="0">
-        <v>0.023449024151277132</v>
+        <v>0.022181049039564849</v>
       </c>
       <c r="C522" s="0">
-        <v>1.9580389263072191</v>
+        <v>1.7520001248669559</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="0">
-        <v>0.16377606210350582</v>
+        <v>0.15848442843295635</v>
       </c>
       <c r="B523" s="0">
-        <v>0.023524348200619726</v>
+        <v>0.02225393935548765</v>
       </c>
       <c r="C523" s="0">
-        <v>1.9706385383621694</v>
+        <v>1.7635337245212139</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="0">
-        <v>0.16408980934891485</v>
+        <v>0.15878803844911146</v>
       </c>
       <c r="B524" s="0">
-        <v>0.023599672249962334</v>
+        <v>0.022326829671410465</v>
       </c>
       <c r="C524" s="0">
-        <v>1.9832785585782826</v>
+        <v>1.7751051631736552</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="0">
-        <v>0.16440355659432385</v>
+        <v>0.15909164846526652</v>
       </c>
       <c r="B525" s="0">
-        <v>0.023674996299304928</v>
+        <v>0.022399719987333266</v>
       </c>
       <c r="C525" s="0">
-        <v>1.9959589869555539</v>
+        <v>1.7867144408242752</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="0">
-        <v>0.16471730383973288</v>
+        <v>0.15939525848142164</v>
       </c>
       <c r="B526" s="0">
-        <v>0.023750320348647536</v>
+        <v>0.02247261030325608</v>
       </c>
       <c r="C526" s="0">
-        <v>2.008679823493988</v>
+        <v>1.7983615574730787</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="0">
-        <v>0.16503105108514191</v>
+        <v>0.15969886849757672</v>
       </c>
       <c r="B527" s="0">
-        <v>0.023825644397990137</v>
+        <v>0.022545500619178888</v>
       </c>
       <c r="C527" s="0">
-        <v>2.0214410681935817</v>
+        <v>1.8100465131200618</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="0">
-        <v>0.16534479833055091</v>
+        <v>0.16000247851373181</v>
       </c>
       <c r="B528" s="0">
-        <v>0.023900968447332739</v>
+        <v>0.022618390935101696</v>
       </c>
       <c r="C528" s="0">
-        <v>2.0342427210543361</v>
+        <v>1.8217693077652259</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="0">
-        <v>0.16565854557595991</v>
+        <v>0.1603060885298869</v>
       </c>
       <c r="B529" s="0">
-        <v>0.023976292496675333</v>
+        <v>0.022691281251024504</v>
       </c>
       <c r="C529" s="0">
-        <v>2.0470847820762495</v>
+        <v>1.8335299414085711</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="0">
-        <v>0.16597229282136891</v>
+        <v>0.16060969854604198</v>
       </c>
       <c r="B530" s="0">
-        <v>0.024051616546017934</v>
+        <v>0.022764171566947312</v>
       </c>
       <c r="C530" s="0">
-        <v>2.0599672512593239</v>
+        <v>1.8453284140500972</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="0">
-        <v>0.16628604006677794</v>
+        <v>0.16091330856219707</v>
       </c>
       <c r="B531" s="0">
-        <v>0.024126940595360535</v>
+        <v>0.02283706188287012</v>
       </c>
       <c r="C531" s="0">
-        <v>2.0728901286035599</v>
+        <v>1.8571647256898043</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="0">
-        <v>0.16659978731218697</v>
+        <v>0.16121691857835216</v>
       </c>
       <c r="B532" s="0">
-        <v>0.024202264644703143</v>
+        <v>0.022909952198792921</v>
       </c>
       <c r="C532" s="0">
-        <v>2.0858534141089575</v>
+        <v>1.8690388763276911</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="0">
-        <v>0.16691353455759597</v>
+        <v>0.16152052859450725</v>
       </c>
       <c r="B533" s="0">
-        <v>0.024277588694045737</v>
+        <v>0.022982842514715728</v>
       </c>
       <c r="C533" s="0">
-        <v>2.0988571077755132</v>
+        <v>1.8809508659637602</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="0">
-        <v>0.167227281803005</v>
+        <v>0.16182413861066233</v>
       </c>
       <c r="B534" s="0">
-        <v>0.024352912743388345</v>
+        <v>0.023055732830638536</v>
       </c>
       <c r="C534" s="0">
-        <v>2.1119012096032317</v>
+        <v>1.8929006945980102</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="0">
-        <v>0.167541029048414</v>
+        <v>0.16212774862681742</v>
       </c>
       <c r="B535" s="0">
-        <v>0.024428236792730939</v>
+        <v>0.023128623146561344</v>
       </c>
       <c r="C535" s="0">
-        <v>2.1249857195921082</v>
+        <v>1.9048883622304411</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="0">
-        <v>0.16785477629382301</v>
+        <v>0.16243135864297251</v>
       </c>
       <c r="B536" s="0">
-        <v>0.02450356084207354</v>
+        <v>0.023201513462484152</v>
       </c>
       <c r="C536" s="0">
-        <v>2.1381106377421468</v>
+        <v>1.9169138688610532</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="0">
-        <v>0.16816852353923203</v>
+        <v>0.16273496865912762</v>
       </c>
       <c r="B537" s="0">
-        <v>0.024578884891416141</v>
+        <v>0.023274403778406966</v>
       </c>
       <c r="C537" s="0">
-        <v>2.1512759640533461</v>
+        <v>1.9289772144898474</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="0">
-        <v>0.16848227078464104</v>
+        <v>0.16303857867528268</v>
       </c>
       <c r="B538" s="0">
-        <v>0.024654208940758742</v>
+        <v>0.023347294094329767</v>
       </c>
       <c r="C538" s="0">
-        <v>2.1644816985257056</v>
+        <v>1.9410783991168201</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="0">
-        <v>0.16879601803005007</v>
+        <v>0.1633421886914378</v>
       </c>
       <c r="B539" s="0">
-        <v>0.024729532990101343</v>
+        <v>0.023420184410252582</v>
       </c>
       <c r="C539" s="0">
-        <v>2.1777278411592258</v>
+        <v>1.9532174227419763</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="0">
-        <v>0.1691097652754591</v>
+        <v>0.16364579870759288</v>
       </c>
       <c r="B540" s="0">
-        <v>0.024804857039443951</v>
+        <v>0.02349307472617539</v>
       </c>
       <c r="C540" s="0">
-        <v>2.1910143919539076</v>
+        <v>1.9653942853653121</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" s="0">
-        <v>0.1694235125208681</v>
+        <v>0.16394940872374797</v>
       </c>
       <c r="B541" s="0">
-        <v>0.024880181088786545</v>
+        <v>0.023565965042098198</v>
       </c>
       <c r="C541" s="0">
-        <v>2.2043413509097474</v>
+        <v>1.977608986986829</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" s="0">
-        <v>0.16973725976627713</v>
+        <v>0.16425301873990306</v>
       </c>
       <c r="B542" s="0">
-        <v>0.024955505138129153</v>
+        <v>0.023638855358021005</v>
       </c>
       <c r="C542" s="0">
-        <v>2.2177087180267505</v>
+        <v>1.9898615276065268</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="0">
-        <v>0.17005100701168613</v>
+        <v>0.16455662875605814</v>
       </c>
       <c r="B543" s="0">
-        <v>0.025030829187471747</v>
+        <v>0.023711745673943813</v>
       </c>
       <c r="C543" s="0">
-        <v>2.2311164933049117</v>
+        <v>2.0021519072244058</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="0">
-        <v>0.17036475425709513</v>
+        <v>0.16486023877221323</v>
       </c>
       <c r="B544" s="0">
-        <v>0.025106153236814349</v>
+        <v>0.023784635989866614</v>
       </c>
       <c r="C544" s="0">
-        <v>2.2445646767442344</v>
+        <v>2.0144801258404641</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="0">
-        <v>0.17067850150250416</v>
+        <v>0.16516384878836832</v>
       </c>
       <c r="B545" s="0">
-        <v>0.02518147728615695</v>
+        <v>0.023857526305789422</v>
       </c>
       <c r="C545" s="0">
-        <v>2.258053268344717</v>
+        <v>2.0268461834547051</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="0">
-        <v>0.17099224874791316</v>
+        <v>0.1654674588045234</v>
       </c>
       <c r="B546" s="0">
-        <v>0.025256801335499551</v>
+        <v>0.02393041662171223</v>
       </c>
       <c r="C546" s="0">
-        <v>2.2715822681063611</v>
+        <v>2.0392500800671267</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="0">
-        <v>0.17130599599332219</v>
+        <v>0.16577106882067849</v>
       </c>
       <c r="B547" s="0">
-        <v>0.025332125384842152</v>
+        <v>0.024003306937635038</v>
       </c>
       <c r="C547" s="0">
-        <v>2.2851516760291655</v>
+        <v>2.0516918156777297</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="0">
-        <v>0.17161974323873119</v>
+        <v>0.16607467883683358</v>
       </c>
       <c r="B548" s="0">
-        <v>0.025407449434184753</v>
+        <v>0.024076197253557846</v>
       </c>
       <c r="C548" s="0">
-        <v>2.2987614921131305</v>
+        <v>2.0641713902865133</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="0">
-        <v>0.17193349048414022</v>
+        <v>0.16637828885298867</v>
       </c>
       <c r="B549" s="0">
-        <v>0.025482773483527354</v>
+        <v>0.024149087569480653</v>
       </c>
       <c r="C549" s="0">
-        <v>2.3124117163582563</v>
+        <v>2.0766888038934783</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="0">
-        <v>0.17224723772954925</v>
+        <v>0.16668189886914378</v>
       </c>
       <c r="B550" s="0">
-        <v>0.025558097532869962</v>
+        <v>0.024221977885403468</v>
       </c>
       <c r="C550" s="0">
-        <v>2.3261023487645436</v>
+        <v>2.0892440564986252</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="0">
-        <v>0.17256098497495823</v>
+        <v>0.16698550888529884</v>
       </c>
       <c r="B551" s="0">
-        <v>0.025633421582212549</v>
+        <v>0.024294868201326269</v>
       </c>
       <c r="C551" s="0">
-        <v>2.3398333893319876</v>
+        <v>2.1018371481019504</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="0">
-        <v>0.17287473222036726</v>
+        <v>0.16728911890145395</v>
       </c>
       <c r="B552" s="0">
-        <v>0.025708745631555157</v>
+        <v>0.024367758517249084</v>
       </c>
       <c r="C552" s="0">
-        <v>2.3536048380605958</v>
+        <v>2.1144680787034593</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="0">
-        <v>0.17318847946577626</v>
+        <v>0.16759272891760901</v>
       </c>
       <c r="B553" s="0">
-        <v>0.025784069680897751</v>
+        <v>0.024440648833171885</v>
       </c>
       <c r="C553" s="0">
-        <v>2.3674166949503621</v>
+        <v>2.127136848303147</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="0">
-        <v>0.17350222671118529</v>
+        <v>0.16789633893376413</v>
       </c>
       <c r="B554" s="0">
-        <v>0.025859393730240359</v>
+        <v>0.024513539149094699</v>
       </c>
       <c r="C554" s="0">
-        <v>2.3812689600012917</v>
+        <v>2.1398434569010179</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="0">
-        <v>0.17381597395659432</v>
+        <v>0.16819994894991921</v>
       </c>
       <c r="B555" s="0">
-        <v>0.02593471777958296</v>
+        <v>0.024586429465017507</v>
       </c>
       <c r="C555" s="0">
-        <v>2.3951616332133807</v>
+        <v>2.1525879044970684</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="0">
-        <v>0.17412972120200332</v>
+        <v>0.1685035589660743</v>
       </c>
       <c r="B556" s="0">
-        <v>0.026010041828925561</v>
+        <v>0.024659319780940308</v>
       </c>
       <c r="C556" s="0">
-        <v>2.4090947145866299</v>
+        <v>2.1653701910912986</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="0">
-        <v>0.17444346844741235</v>
+        <v>0.16880716898222939</v>
       </c>
       <c r="B557" s="0">
-        <v>0.026085365878268162</v>
+        <v>0.024732210096863116</v>
       </c>
       <c r="C557" s="0">
-        <v>2.4230682041210399</v>
+        <v>2.1781903166837111</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="0">
-        <v>0.17475721569282135</v>
+        <v>0.16911077899838448</v>
       </c>
       <c r="B558" s="0">
-        <v>0.026160689927610763</v>
+        <v>0.024805100412785924</v>
       </c>
       <c r="C558" s="0">
-        <v>2.4370821018166105</v>
+        <v>2.1910482812743051</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="0">
-        <v>0.17507096293823035</v>
+        <v>0.16941438901453956</v>
       </c>
       <c r="B559" s="0">
-        <v>0.026236013976953357</v>
+        <v>0.024877990728708731</v>
       </c>
       <c r="C559" s="0">
-        <v>2.45113640767334</v>
+        <v>2.20394408486308</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="0">
-        <v>0.17538471018363938</v>
+        <v>0.16971799903069465</v>
       </c>
       <c r="B560" s="0">
-        <v>0.026311338026295965</v>
+        <v>0.024950881044631539</v>
       </c>
       <c r="C560" s="0">
-        <v>2.4652311216912319</v>
+        <v>2.2168777274500355</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="0">
-        <v>0.17569845742904838</v>
+        <v>0.17002160904684974</v>
       </c>
       <c r="B561" s="0">
-        <v>0.02638666207563856</v>
+        <v>0.025023771360554347</v>
       </c>
       <c r="C561" s="0">
-        <v>2.4793662438702828</v>
+        <v>2.229849209035172</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" s="0">
-        <v>0.17601220467445741</v>
+        <v>0.17032521906300482</v>
       </c>
       <c r="B562" s="0">
-        <v>0.026461986124981168</v>
+        <v>0.025096661676477155</v>
       </c>
       <c r="C562" s="0">
-        <v>2.4935417742104966</v>
+        <v>2.2428585296184895</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" s="0">
-        <v>0.17632595191986644</v>
+        <v>0.17062882907915994</v>
       </c>
       <c r="B563" s="0">
-        <v>0.026537310174323769</v>
+        <v>0.02516955199239997</v>
       </c>
       <c r="C563" s="0">
-        <v>2.5077577127118698</v>
+        <v>2.2559056891999889</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" s="0">
-        <v>0.17663969916527544</v>
+        <v>0.170932439095315</v>
       </c>
       <c r="B564" s="0">
-        <v>0.02661263422366637</v>
+        <v>0.025242442308322771</v>
       </c>
       <c r="C564" s="0">
-        <v>2.5220140593744036</v>
+        <v>2.2689906877796675</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" s="0">
-        <v>0.17695344641068447</v>
+        <v>0.17123604911147011</v>
       </c>
       <c r="B565" s="0">
-        <v>0.026687958273008971</v>
+        <v>0.025315332624245585</v>
       </c>
       <c r="C565" s="0">
-        <v>2.5363108141980977</v>
+        <v>2.2821135253575284</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="0">
-        <v>0.17726719365609345</v>
+        <v>0.17153965912762517</v>
       </c>
       <c r="B566" s="0">
-        <v>0.026763282322351565</v>
+        <v>0.025388222940168386</v>
       </c>
       <c r="C566" s="0">
-        <v>2.5506479771829511</v>
+        <v>2.2952742019335695</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" s="0">
-        <v>0.17758094090150248</v>
+        <v>0.17184326914378026</v>
       </c>
       <c r="B567" s="0">
-        <v>0.026838606371694166</v>
+        <v>0.025461113256091194</v>
       </c>
       <c r="C567" s="0">
-        <v>2.5650255483289666</v>
+        <v>2.3084727175077915</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" s="0">
-        <v>0.17789468814691151</v>
+        <v>0.17214687915993537</v>
       </c>
       <c r="B568" s="0">
-        <v>0.026913930421036774</v>
+        <v>0.025534003572014002</v>
       </c>
       <c r="C568" s="0">
-        <v>2.5794435276361436</v>
+        <v>2.3217090720801949</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" s="0">
-        <v>0.17820843539232051</v>
+        <v>0.17245048917609043</v>
       </c>
       <c r="B569" s="0">
-        <v>0.026989254470379368</v>
+        <v>0.025606893887936803</v>
       </c>
       <c r="C569" s="0">
-        <v>2.5939019151044787</v>
+        <v>2.3349832656507781</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" s="0">
-        <v>0.17852218263772954</v>
+        <v>0.17275409919224555</v>
       </c>
       <c r="B570" s="0">
-        <v>0.027064578519721976</v>
+        <v>0.025679784203859617</v>
       </c>
       <c r="C570" s="0">
-        <v>2.6084007107339771</v>
+        <v>2.3482952982195449</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" s="0">
-        <v>0.17883592988313854</v>
+        <v>0.17305770920840061</v>
       </c>
       <c r="B571" s="0">
-        <v>0.02713990256906457</v>
+        <v>0.025752674519782418</v>
       </c>
       <c r="C571" s="0">
-        <v>2.622939914524633</v>
+        <v>2.3616451697864895</v>
       </c>
     </row>
     <row r="572">
       <c r="A572" s="0">
-        <v>0.17914967712854757</v>
+        <v>0.17336131922455572</v>
       </c>
       <c r="B572" s="0">
-        <v>0.027215226618407178</v>
+        <v>0.025825564835705233</v>
       </c>
       <c r="C572" s="0">
-        <v>2.6375195264764524</v>
+        <v>2.3750328803516183</v>
       </c>
     </row>
     <row r="573">
       <c r="A573" s="0">
-        <v>0.17946342437395657</v>
+        <v>0.17366492924071081</v>
       </c>
       <c r="B573" s="0">
-        <v>0.027290550667749779</v>
+        <v>0.025898455151628041</v>
       </c>
       <c r="C573" s="0">
-        <v>2.6521395465894311</v>
+        <v>2.3884584299149267</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" s="0">
-        <v>0.17977717161936557</v>
+        <v>0.1739685392568659</v>
       </c>
       <c r="B574" s="0">
-        <v>0.027365874717092374</v>
+        <v>0.025971345467550849</v>
       </c>
       <c r="C574" s="0">
-        <v>2.6667999748635687</v>
+        <v>2.4019218184764157</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" s="0">
-        <v>0.1800909188647746</v>
+        <v>0.17427214927302098</v>
       </c>
       <c r="B575" s="0">
-        <v>0.027441198766434982</v>
+        <v>0.026044235783473656</v>
       </c>
       <c r="C575" s="0">
-        <v>2.6815008112988692</v>
+        <v>2.4154230460360862</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="0">
-        <v>0.18040466611018363</v>
+        <v>0.17457575928917607</v>
       </c>
       <c r="B576" s="0">
-        <v>0.027516522815777583</v>
+        <v>0.026117126099396464</v>
       </c>
       <c r="C576" s="0">
-        <v>2.6962420558953291</v>
+        <v>2.4289621125939371</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="0">
-        <v>0.18071841335559263</v>
+        <v>0.17487936930533116</v>
       </c>
       <c r="B577" s="0">
-        <v>0.027591846865120184</v>
+        <v>0.026190016415319272</v>
       </c>
       <c r="C577" s="0">
-        <v>2.7110237086529501</v>
+        <v>2.4425390181499696</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="0">
-        <v>0.18103216060100166</v>
+        <v>0.17518297932148624</v>
       </c>
       <c r="B578" s="0">
-        <v>0.027667170914462785</v>
+        <v>0.02626290673124208</v>
       </c>
       <c r="C578" s="0">
-        <v>2.7258457695717313</v>
+        <v>2.4561537627041825</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" s="0">
-        <v>0.18134590784641066</v>
+        <v>0.17548658933764133</v>
       </c>
       <c r="B579" s="0">
-        <v>0.027742494963805386</v>
+        <v>0.026335797047164888</v>
       </c>
       <c r="C579" s="0">
-        <v>2.7407082386516728</v>
+        <v>2.4698063462565769</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" s="0">
-        <v>0.18165965509181969</v>
+        <v>0.17579019935379642</v>
       </c>
       <c r="B580" s="0">
-        <v>0.027817819013147987</v>
+        <v>0.026408687363087696</v>
       </c>
       <c r="C580" s="0">
-        <v>2.7556111158927754</v>
+        <v>2.4834967688071519</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" s="0">
-        <v>0.1819734023372287</v>
+        <v>0.17609380936995153</v>
       </c>
       <c r="B581" s="0">
-        <v>0.027893143062490588</v>
+        <v>0.026481577679010503</v>
       </c>
       <c r="C581" s="0">
-        <v>2.7705544012950383</v>
+        <v>2.4972250303559078</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" s="0">
-        <v>0.1822871495826377</v>
+        <v>0.17639741938610659</v>
       </c>
       <c r="B582" s="0">
-        <v>0.027968467111833182</v>
+        <v>0.026554467994933304</v>
       </c>
       <c r="C582" s="0">
-        <v>2.7855380948584601</v>
+        <v>2.5109911309028439</v>
       </c>
     </row>
     <row r="583">
       <c r="A583" s="0">
-        <v>0.18260089682804673</v>
+        <v>0.17670102940226171</v>
       </c>
       <c r="B583" s="0">
-        <v>0.02804379116117579</v>
+        <v>0.026627358310856119</v>
       </c>
       <c r="C583" s="0">
-        <v>2.8005621965830456</v>
+        <v>2.5247950704479632</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" s="0">
-        <v>0.18291464407345573</v>
+        <v>0.17700463941841677</v>
       </c>
       <c r="B584" s="0">
-        <v>0.028119115210518384</v>
+        <v>0.02670024862677892</v>
       </c>
       <c r="C584" s="0">
-        <v>2.8156267064687888</v>
+        <v>2.5386368489912608</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" s="0">
-        <v>0.18322839131886476</v>
+        <v>0.17730824943457188</v>
       </c>
       <c r="B585" s="0">
-        <v>0.028194439259860992</v>
+        <v>0.026773138942701735</v>
       </c>
       <c r="C585" s="0">
-        <v>2.8307316245156953</v>
+        <v>2.5525164665327424</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" s="0">
-        <v>0.18354213856427379</v>
+        <v>0.17761185945072697</v>
       </c>
       <c r="B586" s="0">
-        <v>0.028269763309203593</v>
+        <v>0.026846029258624542</v>
       </c>
       <c r="C586" s="0">
-        <v>2.8458769507237607</v>
+        <v>2.5664339230724034</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" s="0">
-        <v>0.18385588580968279</v>
+        <v>0.17791546946688205</v>
       </c>
       <c r="B587" s="0">
-        <v>0.028345087358546194</v>
+        <v>0.02691891957454735</v>
       </c>
       <c r="C587" s="0">
-        <v>2.8610626850929868</v>
+        <v>2.5803892186102453</v>
       </c>
     </row>
     <row r="588">
       <c r="A588" s="0">
-        <v>0.18416963305509179</v>
+        <v>0.17821907948303714</v>
       </c>
       <c r="B588" s="0">
-        <v>0.028420411407888788</v>
+        <v>0.026991809890470158</v>
       </c>
       <c r="C588" s="0">
-        <v>2.8762888276233722</v>
+        <v>2.5943823531462682</v>
       </c>
     </row>
     <row r="589">
       <c r="A589" s="0">
-        <v>0.18448338030050079</v>
+        <v>0.17852268949919223</v>
       </c>
       <c r="B589" s="0">
-        <v>0.028495735457231389</v>
+        <v>0.027064700206392966</v>
       </c>
       <c r="C589" s="0">
-        <v>2.8915553783149193</v>
+        <v>2.6084133266804721</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" s="0">
-        <v>0.18479712754590982</v>
+        <v>0.17882629951534732</v>
       </c>
       <c r="B590" s="0">
-        <v>0.02857105950657399</v>
+        <v>0.027137590522315774</v>
       </c>
       <c r="C590" s="0">
-        <v>2.9068623371676261</v>
+        <v>2.622482139212857</v>
       </c>
     </row>
     <row r="591">
       <c r="A591" s="0">
-        <v>0.18511087479131885</v>
+        <v>0.1791299095315024</v>
       </c>
       <c r="B591" s="0">
-        <v>0.028646383555916598</v>
+        <v>0.027210480838238582</v>
       </c>
       <c r="C591" s="0">
-        <v>2.9222097041814963</v>
+        <v>2.6365887907434229</v>
       </c>
     </row>
     <row r="592">
       <c r="A592" s="0">
-        <v>0.18542462203672785</v>
+        <v>0.17943351954765749</v>
       </c>
       <c r="B592" s="0">
-        <v>0.028721707605259193</v>
+        <v>0.027283371154161389</v>
       </c>
       <c r="C592" s="0">
-        <v>2.9375974793565236</v>
+        <v>2.6507332812721698</v>
       </c>
     </row>
     <row r="593">
       <c r="A593" s="0">
-        <v>0.18573836928213688</v>
+        <v>0.17973712956381258</v>
       </c>
       <c r="B593" s="0">
-        <v>0.028797031654601801</v>
+        <v>0.02735626147008419</v>
       </c>
       <c r="C593" s="0">
-        <v>2.9530256626927143</v>
+        <v>2.6649156107990963</v>
       </c>
     </row>
     <row r="594">
       <c r="A594" s="0">
-        <v>0.18605211652754591</v>
+        <v>0.18004073957996769</v>
       </c>
       <c r="B594" s="0">
-        <v>0.028872355703944402</v>
+        <v>0.027429151786007005</v>
       </c>
       <c r="C594" s="0">
-        <v>2.9684942541900643</v>
+        <v>2.6791357793242065</v>
       </c>
     </row>
     <row r="595">
       <c r="A595" s="0">
-        <v>0.18636586377295492</v>
+        <v>0.18034434959612275</v>
       </c>
       <c r="B595" s="0">
-        <v>0.028947679753287003</v>
+        <v>0.027502042101929806</v>
       </c>
       <c r="C595" s="0">
-        <v>2.9840032538485746</v>
+        <v>2.6933937868474951</v>
       </c>
     </row>
     <row r="596">
       <c r="A596" s="0">
-        <v>0.18667961101836392</v>
+        <v>0.18064795961227786</v>
       </c>
       <c r="B596" s="0">
-        <v>0.029023003802629597</v>
+        <v>0.027574932417852621</v>
       </c>
       <c r="C596" s="0">
-        <v>2.9995526616682442</v>
+        <v>2.7076896333689673</v>
       </c>
     </row>
     <row r="597">
       <c r="A597" s="0">
-        <v>0.18699335826377292</v>
+        <v>0.18095156962843292</v>
       </c>
       <c r="B597" s="0">
-        <v>0.029098327851972198</v>
+        <v>0.027647822733775421</v>
       </c>
       <c r="C597" s="0">
-        <v>3.0151424776490758</v>
+        <v>2.7220233188886178</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" s="0">
-        <v>0.18730710550918195</v>
+        <v>0.18125517964458804</v>
       </c>
       <c r="B598" s="0">
-        <v>0.029173651901314799</v>
+        <v>0.027720713049698236</v>
       </c>
       <c r="C598" s="0">
-        <v>3.0307727017910677</v>
+        <v>2.736394843406452</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" s="0">
-        <v>0.18762085275459098</v>
+        <v>0.18155878966074313</v>
       </c>
       <c r="B599" s="0">
-        <v>0.029248975950657407</v>
+        <v>0.027793603365621044</v>
       </c>
       <c r="C599" s="0">
-        <v>3.0464433340942221</v>
+        <v>2.7508042069224659</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" s="0">
+        <v>0.18186239967689821</v>
+      </c>
+      <c r="B600" s="0">
+        <v>0.027866493681543852</v>
+      </c>
+      <c r="C600" s="0">
+        <v>2.7652514094366607</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="0">
+        <v>0.1821660096930533</v>
+      </c>
+      <c r="B601" s="0">
+        <v>0.02793938399746666</v>
+      </c>
+      <c r="C601" s="0">
+        <v>2.7797364509490361</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="0">
+        <v>0.18246961970920836</v>
+      </c>
+      <c r="B602" s="0">
+        <v>0.02801227431338946</v>
+      </c>
+      <c r="C602" s="0">
+        <v>2.7942593314595916</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" s="0">
+        <v>0.18277322972536347</v>
+      </c>
+      <c r="B603" s="0">
+        <v>0.028085164629312275</v>
+      </c>
+      <c r="C603" s="0">
+        <v>2.8088200509683308</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" s="0">
+        <v>0.18307683974151856</v>
+      </c>
+      <c r="B604" s="0">
+        <v>0.028158054945235083</v>
+      </c>
+      <c r="C604" s="0">
+        <v>2.8234186094752492</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" s="0">
+        <v>0.18338044975767365</v>
+      </c>
+      <c r="B605" s="0">
+        <v>0.028230945261157884</v>
+      </c>
+      <c r="C605" s="0">
+        <v>2.8380550069803476</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" s="0">
+        <v>0.18368405977382873</v>
+      </c>
+      <c r="B606" s="0">
+        <v>0.028303835577080692</v>
+      </c>
+      <c r="C606" s="0">
+        <v>2.852729243483628</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="0">
+        <v>0.18398766978998382</v>
+      </c>
+      <c r="B607" s="0">
+        <v>0.0283767258930035</v>
+      </c>
+      <c r="C607" s="0">
+        <v>2.8674413189850898</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" s="0">
+        <v>0.18429127980613891</v>
+      </c>
+      <c r="B608" s="0">
+        <v>0.028449616208926307</v>
+      </c>
+      <c r="C608" s="0">
+        <v>2.8821912334847322</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="0">
+        <v>0.18459488982229402</v>
+      </c>
+      <c r="B609" s="0">
+        <v>0.028522506524849122</v>
+      </c>
+      <c r="C609" s="0">
+        <v>2.8969789869825573</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" s="0">
+        <v>0.18489849983844908</v>
+      </c>
+      <c r="B610" s="0">
+        <v>0.028595396840771923</v>
+      </c>
+      <c r="C610" s="0">
+        <v>2.9118045794785603</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" s="0">
+        <v>0.18520210985460417</v>
+      </c>
+      <c r="B611" s="0">
+        <v>0.028668287156694731</v>
+      </c>
+      <c r="C611" s="0">
+        <v>2.9266680109727456</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" s="0">
+        <v>0.18550571987075928</v>
+      </c>
+      <c r="B612" s="0">
+        <v>0.028741177472617546</v>
+      </c>
+      <c r="C612" s="0">
+        <v>2.9415692814651138</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" s="0">
+        <v>0.18580932988691434</v>
+      </c>
+      <c r="B613" s="0">
+        <v>0.028814067788540346</v>
+      </c>
+      <c r="C613" s="0">
+        <v>2.9565083909556598</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" s="0">
+        <v>0.18611293990306946</v>
+      </c>
+      <c r="B614" s="0">
+        <v>0.028886958104463161</v>
+      </c>
+      <c r="C614" s="0">
+        <v>2.9714853394443899</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" s="0">
+        <v>0.18641654991922452</v>
+      </c>
+      <c r="B615" s="0">
+        <v>0.028959848420385962</v>
+      </c>
+      <c r="C615" s="0">
+        <v>2.9865001269312979</v>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" s="0">
+        <v>0.18672015993537963</v>
+      </c>
+      <c r="B616" s="0">
+        <v>0.029032738736308777</v>
+      </c>
+      <c r="C616" s="0">
+        <v>3.0015527534163899</v>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" s="0">
+        <v>0.18702376995153472</v>
+      </c>
+      <c r="B617" s="0">
+        <v>0.029105629052231578</v>
+      </c>
+      <c r="C617" s="0">
+        <v>3.0166432188996595</v>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" s="0">
+        <v>0.18732737996768981</v>
+      </c>
+      <c r="B618" s="0">
+        <v>0.029178519368154386</v>
+      </c>
+      <c r="C618" s="0">
+        <v>3.0317715233811122</v>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" s="0">
+        <v>0.18763098998384489</v>
+      </c>
+      <c r="B619" s="0">
+        <v>0.029251409684077193</v>
+      </c>
+      <c r="C619" s="0">
+        <v>3.0469376668607455</v>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" s="0">
         <v>0.18793459999999998</v>
       </c>
-      <c r="B600" s="0">
+      <c r="B620" s="0">
         <v>0.029324300000000001</v>
       </c>
-      <c r="C600" s="0">
-        <v>3.0621543745585336</v>
+      <c r="C620" s="0">
+        <v>3.0621416493385598</v>
       </c>
     </row>
   </sheetData>
